--- a/artfynd/A 58862-2024 artfynd.xlsx
+++ b/artfynd/A 58862-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127148032</v>
       </c>
       <c r="B2" t="n">
-        <v>97245</v>
+        <v>97320</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127148067</v>
       </c>
       <c r="B3" t="n">
-        <v>79059</v>
+        <v>79090</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>127148041</v>
       </c>
       <c r="B4" t="n">
-        <v>97245</v>
+        <v>97320</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>127148039</v>
       </c>
       <c r="B6" t="n">
-        <v>97245</v>
+        <v>97320</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>127148036</v>
       </c>
       <c r="B7" t="n">
-        <v>97245</v>
+        <v>97320</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>127148059</v>
       </c>
       <c r="B8" t="n">
-        <v>92535</v>
+        <v>92609</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1367,10 +1367,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127148033</v>
+        <v>127148038</v>
       </c>
       <c r="B9" t="n">
-        <v>97245</v>
+        <v>97320</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1402,10 +1402,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>718773</v>
+        <v>718694</v>
       </c>
       <c r="R9" t="n">
-        <v>7284302</v>
+        <v>7284325</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1464,10 +1464,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127148038</v>
+        <v>127148033</v>
       </c>
       <c r="B10" t="n">
-        <v>97245</v>
+        <v>97320</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>718694</v>
+        <v>718773</v>
       </c>
       <c r="R10" t="n">
-        <v>7284325</v>
+        <v>7284302</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1564,7 +1564,7 @@
         <v>127148063</v>
       </c>
       <c r="B11" t="n">
-        <v>92535</v>
+        <v>92609</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1658,10 +1658,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127148068</v>
+        <v>127148051</v>
       </c>
       <c r="B12" t="n">
-        <v>78386</v>
+        <v>78678</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1669,21 +1669,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1693,10 +1693,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>718777</v>
+        <v>718726</v>
       </c>
       <c r="R12" t="n">
-        <v>7284375</v>
+        <v>7284409</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1755,10 +1755,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127148051</v>
+        <v>127148068</v>
       </c>
       <c r="B13" t="n">
-        <v>78647</v>
+        <v>78417</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1766,21 +1766,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>718726</v>
+        <v>718777</v>
       </c>
       <c r="R13" t="n">
-        <v>7284409</v>
+        <v>7284375</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1855,7 +1855,7 @@
         <v>127148040</v>
       </c>
       <c r="B14" t="n">
-        <v>97245</v>
+        <v>97320</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         <v>127148046</v>
       </c>
       <c r="B15" t="n">
-        <v>78739</v>
+        <v>78770</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2046,10 +2046,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127148045</v>
+        <v>127148062</v>
       </c>
       <c r="B16" t="n">
-        <v>80111</v>
+        <v>92609</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2057,21 +2057,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6461</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>718709</v>
+        <v>718734</v>
       </c>
       <c r="R16" t="n">
-        <v>7284346</v>
+        <v>7284278</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2143,32 +2143,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127148062</v>
+        <v>127148031</v>
       </c>
       <c r="B17" t="n">
-        <v>92535</v>
+        <v>79090</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>864</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>718734</v>
+        <v>718770</v>
       </c>
       <c r="R17" t="n">
-        <v>7284278</v>
+        <v>7284311</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2222,6 +2222,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2240,32 +2241,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127148031</v>
+        <v>127148045</v>
       </c>
       <c r="B18" t="n">
-        <v>79059</v>
+        <v>80142</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>864</v>
+        <v>6461</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2275,10 +2276,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>718770</v>
+        <v>718709</v>
       </c>
       <c r="R18" t="n">
-        <v>7284311</v>
+        <v>7284346</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2319,7 +2320,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2341,7 +2341,7 @@
         <v>127148042</v>
       </c>
       <c r="B19" t="n">
-        <v>97245</v>
+        <v>97320</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2435,10 +2435,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127148065</v>
+        <v>127148054</v>
       </c>
       <c r="B20" t="n">
-        <v>92535</v>
+        <v>92609</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2470,10 +2470,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>718669</v>
+        <v>718747</v>
       </c>
       <c r="R20" t="n">
-        <v>7284342</v>
+        <v>7284415</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2532,32 +2532,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127148021</v>
+        <v>127148065</v>
       </c>
       <c r="B21" t="n">
-        <v>79598</v>
+        <v>92609</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>718756</v>
+        <v>718669</v>
       </c>
       <c r="R21" t="n">
-        <v>7284289</v>
+        <v>7284342</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2632,7 +2632,7 @@
         <v>127148034</v>
       </c>
       <c r="B22" t="n">
-        <v>97245</v>
+        <v>97320</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2726,32 +2726,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127148054</v>
+        <v>127148021</v>
       </c>
       <c r="B23" t="n">
-        <v>92535</v>
+        <v>79629</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2761,10 +2761,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>718747</v>
+        <v>718756</v>
       </c>
       <c r="R23" t="n">
-        <v>7284415</v>
+        <v>7284289</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2826,7 +2826,7 @@
         <v>127148058</v>
       </c>
       <c r="B24" t="n">
-        <v>92535</v>
+        <v>92609</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>127148057</v>
       </c>
       <c r="B25" t="n">
-        <v>92535</v>
+        <v>92609</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3017,10 +3017,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127148060</v>
+        <v>127148064</v>
       </c>
       <c r="B26" t="n">
-        <v>92535</v>
+        <v>92609</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3052,10 +3052,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>718731</v>
+        <v>718686</v>
       </c>
       <c r="R26" t="n">
-        <v>7284349</v>
+        <v>7284325</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3114,10 +3114,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127148064</v>
+        <v>127148060</v>
       </c>
       <c r="B27" t="n">
-        <v>92535</v>
+        <v>92609</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3149,10 +3149,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>718686</v>
+        <v>718731</v>
       </c>
       <c r="R27" t="n">
-        <v>7284325</v>
+        <v>7284349</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3214,7 +3214,7 @@
         <v>127148056</v>
       </c>
       <c r="B28" t="n">
-        <v>92535</v>
+        <v>92609</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>127148055</v>
       </c>
       <c r="B29" t="n">
-        <v>92535</v>
+        <v>92609</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3405,10 +3405,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127148043</v>
+        <v>127148061</v>
       </c>
       <c r="B30" t="n">
-        <v>97245</v>
+        <v>92609</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3416,21 +3416,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3440,10 +3440,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>718667</v>
+        <v>718771</v>
       </c>
       <c r="R30" t="n">
-        <v>7284313</v>
+        <v>7284306</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3502,32 +3502,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127148061</v>
+        <v>127148020</v>
       </c>
       <c r="B31" t="n">
-        <v>92535</v>
+        <v>79629</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3537,10 +3537,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>718771</v>
+        <v>718765</v>
       </c>
       <c r="R31" t="n">
-        <v>7284306</v>
+        <v>7284389</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3599,32 +3599,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127148020</v>
+        <v>127148043</v>
       </c>
       <c r="B32" t="n">
-        <v>79598</v>
+        <v>97320</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>221941</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3634,10 +3634,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>718765</v>
+        <v>718667</v>
       </c>
       <c r="R32" t="n">
-        <v>7284389</v>
+        <v>7284313</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3699,7 +3699,7 @@
         <v>127148035</v>
       </c>
       <c r="B33" t="n">
-        <v>97245</v>
+        <v>97320</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 58862-2024 artfynd.xlsx
+++ b/artfynd/A 58862-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127148032</v>
       </c>
       <c r="B2" t="n">
-        <v>97320</v>
+        <v>97326</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127148067</v>
       </c>
       <c r="B3" t="n">
-        <v>79090</v>
+        <v>79093</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>127148041</v>
       </c>
       <c r="B4" t="n">
-        <v>97320</v>
+        <v>97326</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -970,49 +970,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127148022</v>
+        <v>127148039</v>
       </c>
       <c r="B5" t="n">
-        <v>57657</v>
+        <v>97326</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Grisberget, Pi lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>718730</v>
+        <v>718678</v>
       </c>
       <c r="R5" t="n">
-        <v>7284454</v>
+        <v>7284335</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1045,11 +1041,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska ringhack över stor del av stammen.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1076,45 +1067,49 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127148039</v>
+        <v>127148022</v>
       </c>
       <c r="B6" t="n">
-        <v>97320</v>
+        <v>57657</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Grisberget, Pi lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>718678</v>
+        <v>718730</v>
       </c>
       <c r="R6" t="n">
-        <v>7284335</v>
+        <v>7284454</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1147,6 +1142,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska ringhack över stor del av stammen.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1173,10 +1173,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127148036</v>
+        <v>127148059</v>
       </c>
       <c r="B7" t="n">
-        <v>97320</v>
+        <v>92615</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1184,21 +1184,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1208,10 +1208,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>718709</v>
+        <v>718785</v>
       </c>
       <c r="R7" t="n">
-        <v>7284315</v>
+        <v>7284347</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1270,10 +1270,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127148059</v>
+        <v>127148036</v>
       </c>
       <c r="B8" t="n">
-        <v>92609</v>
+        <v>97326</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1281,21 +1281,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1305,10 +1305,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>718785</v>
+        <v>718709</v>
       </c>
       <c r="R8" t="n">
-        <v>7284347</v>
+        <v>7284315</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1370,7 +1370,7 @@
         <v>127148038</v>
       </c>
       <c r="B9" t="n">
-        <v>97320</v>
+        <v>97326</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>127148033</v>
       </c>
       <c r="B10" t="n">
-        <v>97320</v>
+        <v>97326</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>127148063</v>
       </c>
       <c r="B11" t="n">
-        <v>92609</v>
+        <v>92615</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>127148051</v>
       </c>
       <c r="B12" t="n">
-        <v>78678</v>
+        <v>78681</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>127148068</v>
       </c>
       <c r="B13" t="n">
-        <v>78417</v>
+        <v>78420</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>127148040</v>
       </c>
       <c r="B14" t="n">
-        <v>97320</v>
+        <v>97326</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         <v>127148046</v>
       </c>
       <c r="B15" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2046,32 +2046,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127148062</v>
+        <v>127148031</v>
       </c>
       <c r="B16" t="n">
-        <v>92609</v>
+        <v>79093</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>4364</v>
+        <v>864</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>718734</v>
+        <v>718770</v>
       </c>
       <c r="R16" t="n">
-        <v>7284278</v>
+        <v>7284311</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2125,6 +2125,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2143,32 +2144,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127148031</v>
+        <v>127148062</v>
       </c>
       <c r="B17" t="n">
-        <v>79090</v>
+        <v>92615</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>864</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2178,10 +2179,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>718770</v>
+        <v>718734</v>
       </c>
       <c r="R17" t="n">
-        <v>7284311</v>
+        <v>7284278</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2222,7 +2223,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2244,7 +2244,7 @@
         <v>127148045</v>
       </c>
       <c r="B18" t="n">
-        <v>80142</v>
+        <v>80145</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
         <v>127148042</v>
       </c>
       <c r="B19" t="n">
-        <v>97320</v>
+        <v>97326</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2438,7 +2438,7 @@
         <v>127148054</v>
       </c>
       <c r="B20" t="n">
-        <v>92609</v>
+        <v>92615</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>127148065</v>
       </c>
       <c r="B21" t="n">
-        <v>92609</v>
+        <v>92615</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2629,32 +2629,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127148034</v>
+        <v>127148021</v>
       </c>
       <c r="B22" t="n">
-        <v>97320</v>
+        <v>79632</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221941</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2664,10 +2664,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>718761</v>
+        <v>718756</v>
       </c>
       <c r="R22" t="n">
-        <v>7284321</v>
+        <v>7284289</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2726,32 +2726,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127148021</v>
+        <v>127148034</v>
       </c>
       <c r="B23" t="n">
-        <v>79629</v>
+        <v>97326</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>221941</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2761,10 +2761,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>718756</v>
+        <v>718761</v>
       </c>
       <c r="R23" t="n">
-        <v>7284289</v>
+        <v>7284321</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2826,7 +2826,7 @@
         <v>127148058</v>
       </c>
       <c r="B24" t="n">
-        <v>92609</v>
+        <v>92615</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>127148057</v>
       </c>
       <c r="B25" t="n">
-        <v>92609</v>
+        <v>92615</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>127148064</v>
       </c>
       <c r="B26" t="n">
-        <v>92609</v>
+        <v>92615</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
         <v>127148060</v>
       </c>
       <c r="B27" t="n">
-        <v>92609</v>
+        <v>92615</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
         <v>127148056</v>
       </c>
       <c r="B28" t="n">
-        <v>92609</v>
+        <v>92615</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>127148055</v>
       </c>
       <c r="B29" t="n">
-        <v>92609</v>
+        <v>92615</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3408,7 +3408,7 @@
         <v>127148061</v>
       </c>
       <c r="B30" t="n">
-        <v>92609</v>
+        <v>92615</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>127148020</v>
       </c>
       <c r="B31" t="n">
-        <v>79629</v>
+        <v>79632</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>127148043</v>
       </c>
       <c r="B32" t="n">
-        <v>97320</v>
+        <v>97326</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>127148035</v>
       </c>
       <c r="B33" t="n">
-        <v>97320</v>
+        <v>97326</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 58862-2024 artfynd.xlsx
+++ b/artfynd/A 58862-2024 artfynd.xlsx
@@ -970,45 +970,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127148039</v>
+        <v>127148022</v>
       </c>
       <c r="B5" t="n">
-        <v>97326</v>
+        <v>57657</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Grisberget, Pi lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>718678</v>
+        <v>718730</v>
       </c>
       <c r="R5" t="n">
-        <v>7284335</v>
+        <v>7284454</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1041,6 +1045,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska ringhack över stor del av stammen.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1067,49 +1076,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127148022</v>
+        <v>127148039</v>
       </c>
       <c r="B6" t="n">
-        <v>57657</v>
+        <v>97326</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Grisberget, Pi lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>718730</v>
+        <v>718678</v>
       </c>
       <c r="R6" t="n">
-        <v>7284454</v>
+        <v>7284335</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1142,11 +1147,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska ringhack över stor del av stammen.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1658,10 +1658,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127148051</v>
+        <v>127148068</v>
       </c>
       <c r="B12" t="n">
-        <v>78681</v>
+        <v>78420</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1669,21 +1669,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1693,10 +1693,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>718726</v>
+        <v>718777</v>
       </c>
       <c r="R12" t="n">
-        <v>7284409</v>
+        <v>7284375</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1755,10 +1755,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127148068</v>
+        <v>127148051</v>
       </c>
       <c r="B13" t="n">
-        <v>78420</v>
+        <v>78681</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1766,21 +1766,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>718777</v>
+        <v>718726</v>
       </c>
       <c r="R13" t="n">
-        <v>7284375</v>
+        <v>7284409</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -2144,10 +2144,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127148062</v>
+        <v>127148045</v>
       </c>
       <c r="B17" t="n">
-        <v>92615</v>
+        <v>80145</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2155,21 +2155,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>6461</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2179,10 +2179,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>718734</v>
+        <v>718709</v>
       </c>
       <c r="R17" t="n">
-        <v>7284278</v>
+        <v>7284346</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2241,10 +2241,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127148045</v>
+        <v>127148062</v>
       </c>
       <c r="B18" t="n">
-        <v>80145</v>
+        <v>92615</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2252,21 +2252,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6461</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2276,10 +2276,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>718709</v>
+        <v>718734</v>
       </c>
       <c r="R18" t="n">
-        <v>7284346</v>
+        <v>7284278</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2435,7 +2435,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127148054</v>
+        <v>127148065</v>
       </c>
       <c r="B20" t="n">
         <v>92615</v>
@@ -2470,10 +2470,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>718747</v>
+        <v>718669</v>
       </c>
       <c r="R20" t="n">
-        <v>7284415</v>
+        <v>7284342</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2532,7 +2532,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127148065</v>
+        <v>127148054</v>
       </c>
       <c r="B21" t="n">
         <v>92615</v>
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>718669</v>
+        <v>718747</v>
       </c>
       <c r="R21" t="n">
-        <v>7284342</v>
+        <v>7284415</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2823,7 +2823,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127148058</v>
+        <v>127148057</v>
       </c>
       <c r="B24" t="n">
         <v>92615</v>
@@ -2858,10 +2858,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>718815</v>
+        <v>718800</v>
       </c>
       <c r="R24" t="n">
-        <v>7284323</v>
+        <v>7284346</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2920,7 +2920,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127148057</v>
+        <v>127148058</v>
       </c>
       <c r="B25" t="n">
         <v>92615</v>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>718800</v>
+        <v>718815</v>
       </c>
       <c r="R25" t="n">
-        <v>7284346</v>
+        <v>7284323</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>

--- a/artfynd/A 58862-2024 artfynd.xlsx
+++ b/artfynd/A 58862-2024 artfynd.xlsx
@@ -2435,10 +2435,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127148065</v>
+        <v>127148034</v>
       </c>
       <c r="B20" t="n">
-        <v>92615</v>
+        <v>97326</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2446,21 +2446,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2470,10 +2470,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>718669</v>
+        <v>718761</v>
       </c>
       <c r="R20" t="n">
-        <v>7284342</v>
+        <v>7284321</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2532,7 +2532,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127148054</v>
+        <v>127148065</v>
       </c>
       <c r="B21" t="n">
         <v>92615</v>
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>718747</v>
+        <v>718669</v>
       </c>
       <c r="R21" t="n">
-        <v>7284415</v>
+        <v>7284342</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2629,32 +2629,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127148021</v>
+        <v>127148054</v>
       </c>
       <c r="B22" t="n">
-        <v>79632</v>
+        <v>92615</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2664,10 +2664,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>718756</v>
+        <v>718747</v>
       </c>
       <c r="R22" t="n">
-        <v>7284289</v>
+        <v>7284415</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2726,32 +2726,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127148034</v>
+        <v>127148021</v>
       </c>
       <c r="B23" t="n">
-        <v>97326</v>
+        <v>79632</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221941</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2761,10 +2761,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>718761</v>
+        <v>718756</v>
       </c>
       <c r="R23" t="n">
-        <v>7284321</v>
+        <v>7284289</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3017,7 +3017,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127148064</v>
+        <v>127148060</v>
       </c>
       <c r="B26" t="n">
         <v>92615</v>
@@ -3052,10 +3052,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>718686</v>
+        <v>718731</v>
       </c>
       <c r="R26" t="n">
-        <v>7284325</v>
+        <v>7284349</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3114,7 +3114,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127148060</v>
+        <v>127148064</v>
       </c>
       <c r="B27" t="n">
         <v>92615</v>
@@ -3149,10 +3149,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>718731</v>
+        <v>718686</v>
       </c>
       <c r="R27" t="n">
-        <v>7284349</v>
+        <v>7284325</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>

--- a/artfynd/A 58862-2024 artfynd.xlsx
+++ b/artfynd/A 58862-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127148032</v>
       </c>
       <c r="B2" t="n">
-        <v>97326</v>
+        <v>97327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>127148041</v>
       </c>
       <c r="B4" t="n">
-        <v>97326</v>
+        <v>97327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>127148039</v>
       </c>
       <c r="B6" t="n">
-        <v>97326</v>
+        <v>97327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>127148059</v>
       </c>
       <c r="B7" t="n">
-        <v>92615</v>
+        <v>92616</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>127148036</v>
       </c>
       <c r="B8" t="n">
-        <v>97326</v>
+        <v>97327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>127148038</v>
       </c>
       <c r="B9" t="n">
-        <v>97326</v>
+        <v>97327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>127148033</v>
       </c>
       <c r="B10" t="n">
-        <v>97326</v>
+        <v>97327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>127148063</v>
       </c>
       <c r="B11" t="n">
-        <v>92615</v>
+        <v>92616</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1658,10 +1658,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127148068</v>
+        <v>127148051</v>
       </c>
       <c r="B12" t="n">
-        <v>78420</v>
+        <v>78681</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1669,21 +1669,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1693,10 +1693,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>718777</v>
+        <v>718726</v>
       </c>
       <c r="R12" t="n">
-        <v>7284375</v>
+        <v>7284409</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1755,10 +1755,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127148051</v>
+        <v>127148068</v>
       </c>
       <c r="B13" t="n">
-        <v>78681</v>
+        <v>78420</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1766,21 +1766,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>718726</v>
+        <v>718777</v>
       </c>
       <c r="R13" t="n">
-        <v>7284409</v>
+        <v>7284375</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1855,7 +1855,7 @@
         <v>127148040</v>
       </c>
       <c r="B14" t="n">
-        <v>97326</v>
+        <v>97327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2144,10 +2144,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127148045</v>
+        <v>127148062</v>
       </c>
       <c r="B17" t="n">
-        <v>80145</v>
+        <v>92616</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2155,21 +2155,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6461</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2179,10 +2179,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>718709</v>
+        <v>718734</v>
       </c>
       <c r="R17" t="n">
-        <v>7284346</v>
+        <v>7284278</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2241,10 +2241,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127148062</v>
+        <v>127148045</v>
       </c>
       <c r="B18" t="n">
-        <v>92615</v>
+        <v>80145</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2252,21 +2252,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>6461</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2276,10 +2276,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>718734</v>
+        <v>718709</v>
       </c>
       <c r="R18" t="n">
-        <v>7284278</v>
+        <v>7284346</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2341,7 +2341,7 @@
         <v>127148042</v>
       </c>
       <c r="B19" t="n">
-        <v>97326</v>
+        <v>97327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2435,32 +2435,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127148034</v>
+        <v>127148021</v>
       </c>
       <c r="B20" t="n">
-        <v>97326</v>
+        <v>79632</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221941</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2470,10 +2470,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>718761</v>
+        <v>718756</v>
       </c>
       <c r="R20" t="n">
-        <v>7284321</v>
+        <v>7284289</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2532,10 +2532,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127148065</v>
+        <v>127148054</v>
       </c>
       <c r="B21" t="n">
-        <v>92615</v>
+        <v>92616</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>718669</v>
+        <v>718747</v>
       </c>
       <c r="R21" t="n">
-        <v>7284342</v>
+        <v>7284415</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2629,10 +2629,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127148054</v>
+        <v>127148065</v>
       </c>
       <c r="B22" t="n">
-        <v>92615</v>
+        <v>92616</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2664,10 +2664,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>718747</v>
+        <v>718669</v>
       </c>
       <c r="R22" t="n">
-        <v>7284415</v>
+        <v>7284342</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2726,32 +2726,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127148021</v>
+        <v>127148034</v>
       </c>
       <c r="B23" t="n">
-        <v>79632</v>
+        <v>97327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>221941</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2761,10 +2761,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>718756</v>
+        <v>718761</v>
       </c>
       <c r="R23" t="n">
-        <v>7284289</v>
+        <v>7284321</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2826,7 +2826,7 @@
         <v>127148057</v>
       </c>
       <c r="B24" t="n">
-        <v>92615</v>
+        <v>92616</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>127148058</v>
       </c>
       <c r="B25" t="n">
-        <v>92615</v>
+        <v>92616</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>127148060</v>
       </c>
       <c r="B26" t="n">
-        <v>92615</v>
+        <v>92616</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
         <v>127148064</v>
       </c>
       <c r="B27" t="n">
-        <v>92615</v>
+        <v>92616</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
         <v>127148056</v>
       </c>
       <c r="B28" t="n">
-        <v>92615</v>
+        <v>92616</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>127148055</v>
       </c>
       <c r="B29" t="n">
-        <v>92615</v>
+        <v>92616</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3405,32 +3405,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127148061</v>
+        <v>127148020</v>
       </c>
       <c r="B30" t="n">
-        <v>92615</v>
+        <v>79632</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3440,10 +3440,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>718771</v>
+        <v>718765</v>
       </c>
       <c r="R30" t="n">
-        <v>7284306</v>
+        <v>7284389</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3502,32 +3502,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127148020</v>
+        <v>127148061</v>
       </c>
       <c r="B31" t="n">
-        <v>79632</v>
+        <v>92616</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3537,10 +3537,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>718765</v>
+        <v>718771</v>
       </c>
       <c r="R31" t="n">
-        <v>7284389</v>
+        <v>7284306</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3602,7 +3602,7 @@
         <v>127148043</v>
       </c>
       <c r="B32" t="n">
-        <v>97326</v>
+        <v>97327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>127148035</v>
       </c>
       <c r="B33" t="n">
-        <v>97326</v>
+        <v>97327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 58862-2024 artfynd.xlsx
+++ b/artfynd/A 58862-2024 artfynd.xlsx
@@ -2046,32 +2046,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127148031</v>
+        <v>127148042</v>
       </c>
       <c r="B16" t="n">
-        <v>79093</v>
+        <v>97327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>864</v>
+        <v>221941</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>718770</v>
+        <v>718677</v>
       </c>
       <c r="R16" t="n">
-        <v>7284311</v>
+        <v>7284327</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2125,7 +2125,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2144,10 +2143,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127148062</v>
+        <v>127148045</v>
       </c>
       <c r="B17" t="n">
-        <v>92616</v>
+        <v>80145</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2155,21 +2154,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>6461</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2179,10 +2178,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>718734</v>
+        <v>718709</v>
       </c>
       <c r="R17" t="n">
-        <v>7284278</v>
+        <v>7284346</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2241,32 +2240,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127148045</v>
+        <v>127148031</v>
       </c>
       <c r="B18" t="n">
-        <v>80145</v>
+        <v>79093</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6461</v>
+        <v>864</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2276,10 +2275,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>718709</v>
+        <v>718770</v>
       </c>
       <c r="R18" t="n">
-        <v>7284346</v>
+        <v>7284311</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2320,6 +2319,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2338,10 +2338,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127148042</v>
+        <v>127148062</v>
       </c>
       <c r="B19" t="n">
-        <v>97327</v>
+        <v>92616</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2349,21 +2349,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2373,10 +2373,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>718677</v>
+        <v>718734</v>
       </c>
       <c r="R19" t="n">
-        <v>7284327</v>
+        <v>7284278</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>

--- a/artfynd/A 58862-2024 artfynd.xlsx
+++ b/artfynd/A 58862-2024 artfynd.xlsx
@@ -772,48 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127148067</v>
+        <v>127148041</v>
       </c>
       <c r="B3" t="n">
-        <v>79093</v>
+        <v>97327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>864</v>
+        <v>221941</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Grisberget, Pi lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>718693</v>
+        <v>718660</v>
       </c>
       <c r="R3" t="n">
-        <v>7284396</v>
+        <v>7284340</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -854,7 +851,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -873,45 +869,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127148041</v>
+        <v>127148067</v>
       </c>
       <c r="B4" t="n">
-        <v>97327</v>
+        <v>79093</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221941</v>
+        <v>864</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Grisberget, Pi lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>718660</v>
+        <v>718693</v>
       </c>
       <c r="R4" t="n">
-        <v>7284340</v>
+        <v>7284396</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -952,6 +951,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -2240,32 +2240,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127148031</v>
+        <v>127148062</v>
       </c>
       <c r="B18" t="n">
-        <v>79093</v>
+        <v>92616</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>864</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2275,10 +2275,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>718770</v>
+        <v>718734</v>
       </c>
       <c r="R18" t="n">
-        <v>7284311</v>
+        <v>7284278</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2319,7 +2319,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2338,32 +2337,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127148062</v>
+        <v>127148031</v>
       </c>
       <c r="B19" t="n">
-        <v>92616</v>
+        <v>79093</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>864</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2373,10 +2372,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>718734</v>
+        <v>718770</v>
       </c>
       <c r="R19" t="n">
-        <v>7284278</v>
+        <v>7284311</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2417,6 +2416,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2435,32 +2435,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127148021</v>
+        <v>127148054</v>
       </c>
       <c r="B20" t="n">
-        <v>79632</v>
+        <v>92616</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2470,10 +2470,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>718756</v>
+        <v>718747</v>
       </c>
       <c r="R20" t="n">
-        <v>7284289</v>
+        <v>7284415</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2532,7 +2532,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127148054</v>
+        <v>127148065</v>
       </c>
       <c r="B21" t="n">
         <v>92616</v>
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>718747</v>
+        <v>718669</v>
       </c>
       <c r="R21" t="n">
-        <v>7284415</v>
+        <v>7284342</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2629,32 +2629,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127148065</v>
+        <v>127148021</v>
       </c>
       <c r="B22" t="n">
-        <v>92616</v>
+        <v>79632</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2664,10 +2664,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>718669</v>
+        <v>718756</v>
       </c>
       <c r="R22" t="n">
-        <v>7284342</v>
+        <v>7284289</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2823,7 +2823,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127148057</v>
+        <v>127148058</v>
       </c>
       <c r="B24" t="n">
         <v>92616</v>
@@ -2858,10 +2858,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>718800</v>
+        <v>718815</v>
       </c>
       <c r="R24" t="n">
-        <v>7284346</v>
+        <v>7284323</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2920,7 +2920,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127148058</v>
+        <v>127148057</v>
       </c>
       <c r="B25" t="n">
         <v>92616</v>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>718815</v>
+        <v>718800</v>
       </c>
       <c r="R25" t="n">
-        <v>7284323</v>
+        <v>7284346</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3405,32 +3405,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127148020</v>
+        <v>127148043</v>
       </c>
       <c r="B30" t="n">
-        <v>79632</v>
+        <v>97327</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>221941</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3440,10 +3440,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>718765</v>
+        <v>718667</v>
       </c>
       <c r="R30" t="n">
-        <v>7284389</v>
+        <v>7284313</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3502,10 +3502,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127148061</v>
+        <v>127148035</v>
       </c>
       <c r="B31" t="n">
-        <v>92616</v>
+        <v>97327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3513,21 +3513,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3537,10 +3537,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>718771</v>
+        <v>718776</v>
       </c>
       <c r="R31" t="n">
-        <v>7284306</v>
+        <v>7284309</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3599,32 +3599,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127148043</v>
+        <v>127148020</v>
       </c>
       <c r="B32" t="n">
-        <v>97327</v>
+        <v>79632</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221941</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3634,10 +3634,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>718667</v>
+        <v>718765</v>
       </c>
       <c r="R32" t="n">
-        <v>7284313</v>
+        <v>7284389</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3696,10 +3696,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127148035</v>
+        <v>127148061</v>
       </c>
       <c r="B33" t="n">
-        <v>97327</v>
+        <v>92616</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3707,21 +3707,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3731,10 +3731,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>718776</v>
+        <v>718771</v>
       </c>
       <c r="R33" t="n">
-        <v>7284309</v>
+        <v>7284306</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>

--- a/artfynd/A 58862-2024 artfynd.xlsx
+++ b/artfynd/A 58862-2024 artfynd.xlsx
@@ -1658,32 +1658,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127148051</v>
+        <v>127148040</v>
       </c>
       <c r="B12" t="n">
-        <v>78681</v>
+        <v>97327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>221941</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1693,10 +1693,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>718726</v>
+        <v>718660</v>
       </c>
       <c r="R12" t="n">
-        <v>7284409</v>
+        <v>7284356</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1852,32 +1852,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127148040</v>
+        <v>127148051</v>
       </c>
       <c r="B14" t="n">
-        <v>97327</v>
+        <v>78681</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221941</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>718660</v>
+        <v>718726</v>
       </c>
       <c r="R14" t="n">
-        <v>7284356</v>
+        <v>7284409</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2046,32 +2046,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127148042</v>
+        <v>127148031</v>
       </c>
       <c r="B16" t="n">
-        <v>97327</v>
+        <v>79093</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221941</v>
+        <v>864</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>718677</v>
+        <v>718770</v>
       </c>
       <c r="R16" t="n">
-        <v>7284327</v>
+        <v>7284311</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2125,6 +2125,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2337,32 +2338,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127148031</v>
+        <v>127148042</v>
       </c>
       <c r="B19" t="n">
-        <v>79093</v>
+        <v>97327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>864</v>
+        <v>221941</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2372,10 +2373,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>718770</v>
+        <v>718677</v>
       </c>
       <c r="R19" t="n">
-        <v>7284311</v>
+        <v>7284327</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2416,7 +2417,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 58862-2024 artfynd.xlsx
+++ b/artfynd/A 58862-2024 artfynd.xlsx
@@ -1755,10 +1755,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127148068</v>
+        <v>127148051</v>
       </c>
       <c r="B13" t="n">
-        <v>78420</v>
+        <v>78681</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1766,21 +1766,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>718777</v>
+        <v>718726</v>
       </c>
       <c r="R13" t="n">
-        <v>7284375</v>
+        <v>7284409</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1852,10 +1852,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127148051</v>
+        <v>127148068</v>
       </c>
       <c r="B14" t="n">
-        <v>78681</v>
+        <v>78420</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1863,21 +1863,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>718726</v>
+        <v>718777</v>
       </c>
       <c r="R14" t="n">
-        <v>7284409</v>
+        <v>7284375</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -3405,32 +3405,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127148043</v>
+        <v>127148020</v>
       </c>
       <c r="B30" t="n">
-        <v>97327</v>
+        <v>79632</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221941</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3440,10 +3440,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>718667</v>
+        <v>718765</v>
       </c>
       <c r="R30" t="n">
-        <v>7284313</v>
+        <v>7284389</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3502,10 +3502,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127148035</v>
+        <v>127148061</v>
       </c>
       <c r="B31" t="n">
-        <v>97327</v>
+        <v>92616</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3513,21 +3513,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3537,10 +3537,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>718776</v>
+        <v>718771</v>
       </c>
       <c r="R31" t="n">
-        <v>7284309</v>
+        <v>7284306</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3599,32 +3599,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127148020</v>
+        <v>127148043</v>
       </c>
       <c r="B32" t="n">
-        <v>79632</v>
+        <v>97327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>221941</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3634,10 +3634,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>718765</v>
+        <v>718667</v>
       </c>
       <c r="R32" t="n">
-        <v>7284389</v>
+        <v>7284313</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3696,10 +3696,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127148061</v>
+        <v>127148035</v>
       </c>
       <c r="B33" t="n">
-        <v>92616</v>
+        <v>97327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3707,21 +3707,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3731,10 +3731,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>718771</v>
+        <v>718776</v>
       </c>
       <c r="R33" t="n">
-        <v>7284306</v>
+        <v>7284309</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>

--- a/artfynd/A 58862-2024 artfynd.xlsx
+++ b/artfynd/A 58862-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127148032</v>
       </c>
       <c r="B2" t="n">
-        <v>97327</v>
+        <v>97331</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,45 +772,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127148041</v>
+        <v>127148067</v>
       </c>
       <c r="B3" t="n">
-        <v>97327</v>
+        <v>79097</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>864</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Grisberget, Pi lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>718660</v>
+        <v>718693</v>
       </c>
       <c r="R3" t="n">
-        <v>7284340</v>
+        <v>7284396</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -851,6 +854,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -869,48 +873,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127148067</v>
+        <v>127148041</v>
       </c>
       <c r="B4" t="n">
-        <v>79093</v>
+        <v>97331</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>864</v>
+        <v>221941</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Grisberget, Pi lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>718693</v>
+        <v>718660</v>
       </c>
       <c r="R4" t="n">
-        <v>7284396</v>
+        <v>7284340</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -951,7 +952,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -973,7 +973,7 @@
         <v>127148022</v>
       </c>
       <c r="B5" t="n">
-        <v>57657</v>
+        <v>57661</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>127148039</v>
       </c>
       <c r="B6" t="n">
-        <v>97327</v>
+        <v>97331</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>127148059</v>
       </c>
       <c r="B7" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>127148036</v>
       </c>
       <c r="B8" t="n">
-        <v>97327</v>
+        <v>97331</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>127148038</v>
       </c>
       <c r="B9" t="n">
-        <v>97327</v>
+        <v>97331</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>127148033</v>
       </c>
       <c r="B10" t="n">
-        <v>97327</v>
+        <v>97331</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>127148063</v>
       </c>
       <c r="B11" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1658,32 +1658,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127148040</v>
+        <v>127148051</v>
       </c>
       <c r="B12" t="n">
-        <v>97327</v>
+        <v>78685</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221941</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1693,10 +1693,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>718660</v>
+        <v>718726</v>
       </c>
       <c r="R12" t="n">
-        <v>7284356</v>
+        <v>7284409</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1755,10 +1755,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127148051</v>
+        <v>127148068</v>
       </c>
       <c r="B13" t="n">
-        <v>78681</v>
+        <v>78424</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1766,21 +1766,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>718726</v>
+        <v>718777</v>
       </c>
       <c r="R13" t="n">
-        <v>7284409</v>
+        <v>7284375</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1852,32 +1852,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127148068</v>
+        <v>127148040</v>
       </c>
       <c r="B14" t="n">
-        <v>78420</v>
+        <v>97331</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6437</v>
+        <v>221941</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>718777</v>
+        <v>718660</v>
       </c>
       <c r="R14" t="n">
-        <v>7284375</v>
+        <v>7284356</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1952,7 +1952,7 @@
         <v>127148046</v>
       </c>
       <c r="B15" t="n">
-        <v>78773</v>
+        <v>78777</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2046,32 +2046,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127148031</v>
+        <v>127148042</v>
       </c>
       <c r="B16" t="n">
-        <v>79093</v>
+        <v>97331</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>864</v>
+        <v>221941</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>718770</v>
+        <v>718677</v>
       </c>
       <c r="R16" t="n">
-        <v>7284311</v>
+        <v>7284327</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2125,7 +2125,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2144,32 +2143,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127148045</v>
+        <v>127148031</v>
       </c>
       <c r="B17" t="n">
-        <v>80145</v>
+        <v>79097</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6461</v>
+        <v>864</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2179,10 +2178,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>718709</v>
+        <v>718770</v>
       </c>
       <c r="R17" t="n">
-        <v>7284346</v>
+        <v>7284311</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2223,6 +2222,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2244,7 +2244,7 @@
         <v>127148062</v>
       </c>
       <c r="B18" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2338,10 +2338,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127148042</v>
+        <v>127148045</v>
       </c>
       <c r="B19" t="n">
-        <v>97327</v>
+        <v>80149</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2349,21 +2349,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221941</v>
+        <v>6461</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2373,10 +2373,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>718677</v>
+        <v>718709</v>
       </c>
       <c r="R19" t="n">
-        <v>7284327</v>
+        <v>7284346</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2435,32 +2435,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127148054</v>
+        <v>127148021</v>
       </c>
       <c r="B20" t="n">
-        <v>92616</v>
+        <v>79636</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2470,10 +2470,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>718747</v>
+        <v>718756</v>
       </c>
       <c r="R20" t="n">
-        <v>7284415</v>
+        <v>7284289</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2532,10 +2532,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127148065</v>
+        <v>127148054</v>
       </c>
       <c r="B21" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>718669</v>
+        <v>718747</v>
       </c>
       <c r="R21" t="n">
-        <v>7284342</v>
+        <v>7284415</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2629,32 +2629,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127148021</v>
+        <v>127148065</v>
       </c>
       <c r="B22" t="n">
-        <v>79632</v>
+        <v>92620</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2664,10 +2664,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>718756</v>
+        <v>718669</v>
       </c>
       <c r="R22" t="n">
-        <v>7284289</v>
+        <v>7284342</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2729,7 +2729,7 @@
         <v>127148034</v>
       </c>
       <c r="B23" t="n">
-        <v>97327</v>
+        <v>97331</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>127148058</v>
       </c>
       <c r="B24" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>127148057</v>
       </c>
       <c r="B25" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>127148060</v>
       </c>
       <c r="B26" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
         <v>127148064</v>
       </c>
       <c r="B27" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
         <v>127148056</v>
       </c>
       <c r="B28" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>127148055</v>
       </c>
       <c r="B29" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3408,7 +3408,7 @@
         <v>127148020</v>
       </c>
       <c r="B30" t="n">
-        <v>79632</v>
+        <v>79636</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>127148061</v>
       </c>
       <c r="B31" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>127148043</v>
       </c>
       <c r="B32" t="n">
-        <v>97327</v>
+        <v>97331</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>127148035</v>
       </c>
       <c r="B33" t="n">
-        <v>97327</v>
+        <v>97331</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3796,7 +3796,7 @@
         <v>127148030</v>
       </c>
       <c r="B34" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 58862-2024 artfynd.xlsx
+++ b/artfynd/A 58862-2024 artfynd.xlsx
@@ -2046,10 +2046,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127148042</v>
+        <v>127148045</v>
       </c>
       <c r="B16" t="n">
-        <v>97331</v>
+        <v>80149</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2057,21 +2057,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221941</v>
+        <v>6461</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>718677</v>
+        <v>718709</v>
       </c>
       <c r="R16" t="n">
-        <v>7284327</v>
+        <v>7284346</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2338,10 +2338,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127148045</v>
+        <v>127148042</v>
       </c>
       <c r="B19" t="n">
-        <v>80149</v>
+        <v>97331</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2349,21 +2349,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6461</v>
+        <v>221941</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2373,10 +2373,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>718709</v>
+        <v>718677</v>
       </c>
       <c r="R19" t="n">
-        <v>7284346</v>
+        <v>7284327</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>

--- a/artfynd/A 58862-2024 artfynd.xlsx
+++ b/artfynd/A 58862-2024 artfynd.xlsx
@@ -772,48 +772,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127148067</v>
+        <v>127148041</v>
       </c>
       <c r="B3" t="n">
-        <v>79097</v>
+        <v>97331</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>864</v>
+        <v>221941</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Grisberget, Pi lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>718693</v>
+        <v>718660</v>
       </c>
       <c r="R3" t="n">
-        <v>7284396</v>
+        <v>7284340</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -854,7 +851,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -873,45 +869,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127148041</v>
+        <v>127148067</v>
       </c>
       <c r="B4" t="n">
-        <v>97331</v>
+        <v>79097</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221941</v>
+        <v>864</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Grisberget, Pi lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>718660</v>
+        <v>718693</v>
       </c>
       <c r="R4" t="n">
-        <v>7284340</v>
+        <v>7284396</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -952,6 +951,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 58862-2024 artfynd.xlsx
+++ b/artfynd/A 58862-2024 artfynd.xlsx
@@ -970,49 +970,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127148022</v>
+        <v>127148039</v>
       </c>
       <c r="B5" t="n">
-        <v>57661</v>
+        <v>97331</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Grisberget, Pi lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>718730</v>
+        <v>718678</v>
       </c>
       <c r="R5" t="n">
-        <v>7284454</v>
+        <v>7284335</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1045,11 +1041,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska ringhack över stor del av stammen.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1076,45 +1067,49 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127148039</v>
+        <v>127148022</v>
       </c>
       <c r="B6" t="n">
-        <v>97331</v>
+        <v>57661</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Grisberget, Pi lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>718678</v>
+        <v>718730</v>
       </c>
       <c r="R6" t="n">
-        <v>7284335</v>
+        <v>7284454</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1147,6 +1142,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska ringhack över stor del av stammen.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -2046,32 +2046,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127148045</v>
+        <v>127148031</v>
       </c>
       <c r="B16" t="n">
-        <v>80149</v>
+        <v>79097</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6461</v>
+        <v>864</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>718709</v>
+        <v>718770</v>
       </c>
       <c r="R16" t="n">
-        <v>7284346</v>
+        <v>7284311</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2125,6 +2125,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2143,32 +2144,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127148031</v>
+        <v>127148045</v>
       </c>
       <c r="B17" t="n">
-        <v>79097</v>
+        <v>80149</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>864</v>
+        <v>6461</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2178,10 +2179,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>718770</v>
+        <v>718709</v>
       </c>
       <c r="R17" t="n">
-        <v>7284311</v>
+        <v>7284346</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2222,7 +2223,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 58862-2024 artfynd.xlsx
+++ b/artfynd/A 58862-2024 artfynd.xlsx
@@ -772,45 +772,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127148041</v>
+        <v>127148067</v>
       </c>
       <c r="B3" t="n">
-        <v>97331</v>
+        <v>79097</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221941</v>
+        <v>864</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Grisberget, Pi lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>718660</v>
+        <v>718693</v>
       </c>
       <c r="R3" t="n">
-        <v>7284340</v>
+        <v>7284396</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -851,6 +854,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -869,48 +873,45 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127148067</v>
+        <v>127148041</v>
       </c>
       <c r="B4" t="n">
-        <v>79097</v>
+        <v>97331</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>864</v>
+        <v>221941</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Grisberget, Pi lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>718693</v>
+        <v>718660</v>
       </c>
       <c r="R4" t="n">
-        <v>7284396</v>
+        <v>7284340</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -951,7 +952,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -970,45 +970,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127148039</v>
+        <v>127148022</v>
       </c>
       <c r="B5" t="n">
-        <v>97331</v>
+        <v>57661</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Grisberget, Pi lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>718678</v>
+        <v>718730</v>
       </c>
       <c r="R5" t="n">
-        <v>7284335</v>
+        <v>7284454</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1041,6 +1045,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska ringhack över stor del av stammen.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1067,49 +1076,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127148022</v>
+        <v>127148039</v>
       </c>
       <c r="B6" t="n">
-        <v>57661</v>
+        <v>97331</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Grisberget, Pi lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>718730</v>
+        <v>718678</v>
       </c>
       <c r="R6" t="n">
-        <v>7284454</v>
+        <v>7284335</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1142,11 +1147,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska ringhack över stor del av stammen.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1658,10 +1658,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127148051</v>
+        <v>127148068</v>
       </c>
       <c r="B12" t="n">
-        <v>78685</v>
+        <v>78424</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1669,21 +1669,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1693,10 +1693,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>718726</v>
+        <v>718777</v>
       </c>
       <c r="R12" t="n">
-        <v>7284409</v>
+        <v>7284375</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1755,32 +1755,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127148068</v>
+        <v>127148040</v>
       </c>
       <c r="B13" t="n">
-        <v>78424</v>
+        <v>97331</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6437</v>
+        <v>221941</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>718777</v>
+        <v>718660</v>
       </c>
       <c r="R13" t="n">
-        <v>7284375</v>
+        <v>7284356</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1852,32 +1852,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127148040</v>
+        <v>127148051</v>
       </c>
       <c r="B14" t="n">
-        <v>97331</v>
+        <v>78685</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221941</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>718660</v>
+        <v>718726</v>
       </c>
       <c r="R14" t="n">
-        <v>7284356</v>
+        <v>7284409</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2046,32 +2046,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127148031</v>
+        <v>127148045</v>
       </c>
       <c r="B16" t="n">
-        <v>79097</v>
+        <v>80149</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>864</v>
+        <v>6461</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>718770</v>
+        <v>718709</v>
       </c>
       <c r="R16" t="n">
-        <v>7284311</v>
+        <v>7284346</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2125,7 +2125,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2144,32 +2143,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127148045</v>
+        <v>127148031</v>
       </c>
       <c r="B17" t="n">
-        <v>80149</v>
+        <v>79097</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6461</v>
+        <v>864</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2179,10 +2178,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>718709</v>
+        <v>718770</v>
       </c>
       <c r="R17" t="n">
-        <v>7284346</v>
+        <v>7284311</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2223,6 +2222,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2435,32 +2435,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127148021</v>
+        <v>127148054</v>
       </c>
       <c r="B20" t="n">
-        <v>79636</v>
+        <v>92620</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2470,10 +2470,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>718756</v>
+        <v>718747</v>
       </c>
       <c r="R20" t="n">
-        <v>7284289</v>
+        <v>7284415</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2532,7 +2532,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127148054</v>
+        <v>127148065</v>
       </c>
       <c r="B21" t="n">
         <v>92620</v>
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>718747</v>
+        <v>718669</v>
       </c>
       <c r="R21" t="n">
-        <v>7284415</v>
+        <v>7284342</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2629,32 +2629,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127148065</v>
+        <v>127148021</v>
       </c>
       <c r="B22" t="n">
-        <v>92620</v>
+        <v>79636</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2664,10 +2664,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>718669</v>
+        <v>718756</v>
       </c>
       <c r="R22" t="n">
-        <v>7284342</v>
+        <v>7284289</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>

--- a/artfynd/A 58862-2024 artfynd.xlsx
+++ b/artfynd/A 58862-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127148032</v>
       </c>
       <c r="B2" t="n">
-        <v>97331</v>
+        <v>97333</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127148067</v>
       </c>
       <c r="B3" t="n">
-        <v>79097</v>
+        <v>79099</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>127148041</v>
       </c>
       <c r="B4" t="n">
-        <v>97331</v>
+        <v>97333</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>127148022</v>
       </c>
       <c r="B5" t="n">
-        <v>57661</v>
+        <v>57663</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>127148039</v>
       </c>
       <c r="B6" t="n">
-        <v>97331</v>
+        <v>97333</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>127148059</v>
       </c>
       <c r="B7" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>127148036</v>
       </c>
       <c r="B8" t="n">
-        <v>97331</v>
+        <v>97333</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>127148038</v>
       </c>
       <c r="B9" t="n">
-        <v>97331</v>
+        <v>97333</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>127148033</v>
       </c>
       <c r="B10" t="n">
-        <v>97331</v>
+        <v>97333</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>127148063</v>
       </c>
       <c r="B11" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1658,10 +1658,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127148068</v>
+        <v>127148051</v>
       </c>
       <c r="B12" t="n">
-        <v>78424</v>
+        <v>78687</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1669,21 +1669,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1693,10 +1693,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>718777</v>
+        <v>718726</v>
       </c>
       <c r="R12" t="n">
-        <v>7284375</v>
+        <v>7284409</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1755,32 +1755,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127148040</v>
+        <v>127148068</v>
       </c>
       <c r="B13" t="n">
-        <v>97331</v>
+        <v>78426</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221941</v>
+        <v>6437</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>718660</v>
+        <v>718777</v>
       </c>
       <c r="R13" t="n">
-        <v>7284356</v>
+        <v>7284375</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1852,32 +1852,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127148051</v>
+        <v>127148040</v>
       </c>
       <c r="B14" t="n">
-        <v>78685</v>
+        <v>97333</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>221941</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>718726</v>
+        <v>718660</v>
       </c>
       <c r="R14" t="n">
-        <v>7284409</v>
+        <v>7284356</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1952,7 +1952,7 @@
         <v>127148046</v>
       </c>
       <c r="B15" t="n">
-        <v>78777</v>
+        <v>78779</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2046,10 +2046,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127148045</v>
+        <v>127148042</v>
       </c>
       <c r="B16" t="n">
-        <v>80149</v>
+        <v>97333</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2057,21 +2057,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6461</v>
+        <v>221941</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>718709</v>
+        <v>718677</v>
       </c>
       <c r="R16" t="n">
-        <v>7284346</v>
+        <v>7284327</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2146,7 +2146,7 @@
         <v>127148031</v>
       </c>
       <c r="B17" t="n">
-        <v>79097</v>
+        <v>79099</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
         <v>127148062</v>
       </c>
       <c r="B18" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2338,10 +2338,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127148042</v>
+        <v>127148045</v>
       </c>
       <c r="B19" t="n">
-        <v>97331</v>
+        <v>80151</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2349,21 +2349,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221941</v>
+        <v>6461</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2373,10 +2373,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>718677</v>
+        <v>718709</v>
       </c>
       <c r="R19" t="n">
-        <v>7284327</v>
+        <v>7284346</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2435,32 +2435,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127148054</v>
+        <v>127148021</v>
       </c>
       <c r="B20" t="n">
-        <v>92620</v>
+        <v>79638</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2470,10 +2470,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>718747</v>
+        <v>718756</v>
       </c>
       <c r="R20" t="n">
-        <v>7284415</v>
+        <v>7284289</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2532,10 +2532,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127148065</v>
+        <v>127148034</v>
       </c>
       <c r="B21" t="n">
-        <v>92620</v>
+        <v>97333</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2543,21 +2543,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>718669</v>
+        <v>718761</v>
       </c>
       <c r="R21" t="n">
-        <v>7284342</v>
+        <v>7284321</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2629,32 +2629,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127148021</v>
+        <v>127148054</v>
       </c>
       <c r="B22" t="n">
-        <v>79636</v>
+        <v>92622</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2664,10 +2664,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>718756</v>
+        <v>718747</v>
       </c>
       <c r="R22" t="n">
-        <v>7284289</v>
+        <v>7284415</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2726,10 +2726,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127148034</v>
+        <v>127148065</v>
       </c>
       <c r="B23" t="n">
-        <v>97331</v>
+        <v>92622</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2737,21 +2737,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2761,10 +2761,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>718761</v>
+        <v>718669</v>
       </c>
       <c r="R23" t="n">
-        <v>7284321</v>
+        <v>7284342</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2826,7 +2826,7 @@
         <v>127148058</v>
       </c>
       <c r="B24" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>127148057</v>
       </c>
       <c r="B25" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>127148060</v>
       </c>
       <c r="B26" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
         <v>127148064</v>
       </c>
       <c r="B27" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
         <v>127148056</v>
       </c>
       <c r="B28" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>127148055</v>
       </c>
       <c r="B29" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3405,32 +3405,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127148020</v>
+        <v>127148061</v>
       </c>
       <c r="B30" t="n">
-        <v>79636</v>
+        <v>92622</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3440,10 +3440,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>718765</v>
+        <v>718771</v>
       </c>
       <c r="R30" t="n">
-        <v>7284389</v>
+        <v>7284306</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3502,32 +3502,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127148061</v>
+        <v>127148020</v>
       </c>
       <c r="B31" t="n">
-        <v>92620</v>
+        <v>79638</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3537,10 +3537,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>718771</v>
+        <v>718765</v>
       </c>
       <c r="R31" t="n">
-        <v>7284306</v>
+        <v>7284389</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3602,7 +3602,7 @@
         <v>127148043</v>
       </c>
       <c r="B32" t="n">
-        <v>97331</v>
+        <v>97333</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>127148035</v>
       </c>
       <c r="B33" t="n">
-        <v>97331</v>
+        <v>97333</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3796,7 +3796,7 @@
         <v>127148030</v>
       </c>
       <c r="B34" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 58862-2024 artfynd.xlsx
+++ b/artfynd/A 58862-2024 artfynd.xlsx
@@ -2046,32 +2046,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127148042</v>
+        <v>127148031</v>
       </c>
       <c r="B16" t="n">
-        <v>97333</v>
+        <v>79099</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221941</v>
+        <v>864</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>718677</v>
+        <v>718770</v>
       </c>
       <c r="R16" t="n">
-        <v>7284327</v>
+        <v>7284311</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2125,6 +2125,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2143,32 +2144,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127148031</v>
+        <v>127148062</v>
       </c>
       <c r="B17" t="n">
-        <v>79099</v>
+        <v>92622</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>864</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2178,10 +2179,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>718770</v>
+        <v>718734</v>
       </c>
       <c r="R17" t="n">
-        <v>7284311</v>
+        <v>7284278</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2222,7 +2223,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2241,10 +2241,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127148062</v>
+        <v>127148045</v>
       </c>
       <c r="B18" t="n">
-        <v>92622</v>
+        <v>80151</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2252,21 +2252,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>6461</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2276,10 +2276,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>718734</v>
+        <v>718709</v>
       </c>
       <c r="R18" t="n">
-        <v>7284278</v>
+        <v>7284346</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2338,10 +2338,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127148045</v>
+        <v>127148042</v>
       </c>
       <c r="B19" t="n">
-        <v>80151</v>
+        <v>97333</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2349,21 +2349,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6461</v>
+        <v>221941</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2373,10 +2373,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>718709</v>
+        <v>718677</v>
       </c>
       <c r="R19" t="n">
-        <v>7284346</v>
+        <v>7284327</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2532,10 +2532,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127148034</v>
+        <v>127148054</v>
       </c>
       <c r="B21" t="n">
-        <v>97333</v>
+        <v>92622</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2543,21 +2543,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>718761</v>
+        <v>718747</v>
       </c>
       <c r="R21" t="n">
-        <v>7284321</v>
+        <v>7284415</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2629,7 +2629,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127148054</v>
+        <v>127148065</v>
       </c>
       <c r="B22" t="n">
         <v>92622</v>
@@ -2664,10 +2664,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>718747</v>
+        <v>718669</v>
       </c>
       <c r="R22" t="n">
-        <v>7284415</v>
+        <v>7284342</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2726,10 +2726,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127148065</v>
+        <v>127148034</v>
       </c>
       <c r="B23" t="n">
-        <v>92622</v>
+        <v>97333</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2737,21 +2737,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2761,10 +2761,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>718669</v>
+        <v>718761</v>
       </c>
       <c r="R23" t="n">
-        <v>7284342</v>
+        <v>7284321</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3017,7 +3017,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127148060</v>
+        <v>127148064</v>
       </c>
       <c r="B26" t="n">
         <v>92622</v>
@@ -3052,10 +3052,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>718731</v>
+        <v>718686</v>
       </c>
       <c r="R26" t="n">
-        <v>7284349</v>
+        <v>7284325</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3114,7 +3114,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127148064</v>
+        <v>127148060</v>
       </c>
       <c r="B27" t="n">
         <v>92622</v>
@@ -3149,10 +3149,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>718686</v>
+        <v>718731</v>
       </c>
       <c r="R27" t="n">
-        <v>7284325</v>
+        <v>7284349</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3405,10 +3405,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127148061</v>
+        <v>127148043</v>
       </c>
       <c r="B30" t="n">
-        <v>92622</v>
+        <v>97333</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3416,21 +3416,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3440,10 +3440,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>718771</v>
+        <v>718667</v>
       </c>
       <c r="R30" t="n">
-        <v>7284306</v>
+        <v>7284313</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3502,32 +3502,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127148020</v>
+        <v>127148035</v>
       </c>
       <c r="B31" t="n">
-        <v>79638</v>
+        <v>97333</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>221941</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3537,10 +3537,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>718765</v>
+        <v>718776</v>
       </c>
       <c r="R31" t="n">
-        <v>7284389</v>
+        <v>7284309</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3599,10 +3599,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127148043</v>
+        <v>127148061</v>
       </c>
       <c r="B32" t="n">
-        <v>97333</v>
+        <v>92622</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3610,21 +3610,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3634,10 +3634,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>718667</v>
+        <v>718771</v>
       </c>
       <c r="R32" t="n">
-        <v>7284313</v>
+        <v>7284306</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3696,32 +3696,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127148035</v>
+        <v>127148020</v>
       </c>
       <c r="B33" t="n">
-        <v>97333</v>
+        <v>79638</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221941</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3731,10 +3731,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>718776</v>
+        <v>718765</v>
       </c>
       <c r="R33" t="n">
-        <v>7284309</v>
+        <v>7284389</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>

--- a/artfynd/A 58862-2024 artfynd.xlsx
+++ b/artfynd/A 58862-2024 artfynd.xlsx
@@ -1173,10 +1173,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127148059</v>
+        <v>127148036</v>
       </c>
       <c r="B7" t="n">
-        <v>92622</v>
+        <v>97333</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1184,21 +1184,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1208,10 +1208,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>718785</v>
+        <v>718709</v>
       </c>
       <c r="R7" t="n">
-        <v>7284347</v>
+        <v>7284315</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1270,10 +1270,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127148036</v>
+        <v>127148059</v>
       </c>
       <c r="B8" t="n">
-        <v>97333</v>
+        <v>92622</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1281,21 +1281,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1305,10 +1305,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>718709</v>
+        <v>718785</v>
       </c>
       <c r="R8" t="n">
-        <v>7284315</v>
+        <v>7284347</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1658,10 +1658,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127148051</v>
+        <v>127148068</v>
       </c>
       <c r="B12" t="n">
-        <v>78687</v>
+        <v>78426</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1669,21 +1669,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1693,10 +1693,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>718726</v>
+        <v>718777</v>
       </c>
       <c r="R12" t="n">
-        <v>7284409</v>
+        <v>7284375</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1755,32 +1755,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127148068</v>
+        <v>127148040</v>
       </c>
       <c r="B13" t="n">
-        <v>78426</v>
+        <v>97333</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6437</v>
+        <v>221941</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>718777</v>
+        <v>718660</v>
       </c>
       <c r="R13" t="n">
-        <v>7284375</v>
+        <v>7284356</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1852,32 +1852,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127148040</v>
+        <v>127148051</v>
       </c>
       <c r="B14" t="n">
-        <v>97333</v>
+        <v>78687</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221941</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>718660</v>
+        <v>718726</v>
       </c>
       <c r="R14" t="n">
-        <v>7284356</v>
+        <v>7284409</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -3405,10 +3405,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127148043</v>
+        <v>127148061</v>
       </c>
       <c r="B30" t="n">
-        <v>97333</v>
+        <v>92622</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3416,21 +3416,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3440,10 +3440,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>718667</v>
+        <v>718771</v>
       </c>
       <c r="R30" t="n">
-        <v>7284313</v>
+        <v>7284306</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3502,32 +3502,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127148035</v>
+        <v>127148020</v>
       </c>
       <c r="B31" t="n">
-        <v>97333</v>
+        <v>79638</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221941</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3537,10 +3537,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>718776</v>
+        <v>718765</v>
       </c>
       <c r="R31" t="n">
-        <v>7284309</v>
+        <v>7284389</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3599,10 +3599,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127148061</v>
+        <v>127148043</v>
       </c>
       <c r="B32" t="n">
-        <v>92622</v>
+        <v>97333</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3610,21 +3610,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3634,10 +3634,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>718771</v>
+        <v>718667</v>
       </c>
       <c r="R32" t="n">
-        <v>7284306</v>
+        <v>7284313</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3696,32 +3696,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127148020</v>
+        <v>127148035</v>
       </c>
       <c r="B33" t="n">
-        <v>79638</v>
+        <v>97333</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>221941</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3731,10 +3731,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>718765</v>
+        <v>718776</v>
       </c>
       <c r="R33" t="n">
-        <v>7284389</v>
+        <v>7284309</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>

--- a/artfynd/A 58862-2024 artfynd.xlsx
+++ b/artfynd/A 58862-2024 artfynd.xlsx
@@ -1173,10 +1173,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127148036</v>
+        <v>127148059</v>
       </c>
       <c r="B7" t="n">
-        <v>97333</v>
+        <v>92622</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1184,21 +1184,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1208,10 +1208,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>718709</v>
+        <v>718785</v>
       </c>
       <c r="R7" t="n">
-        <v>7284315</v>
+        <v>7284347</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1270,10 +1270,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127148059</v>
+        <v>127148036</v>
       </c>
       <c r="B8" t="n">
-        <v>92622</v>
+        <v>97333</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1281,21 +1281,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1305,10 +1305,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>718785</v>
+        <v>718709</v>
       </c>
       <c r="R8" t="n">
-        <v>7284347</v>
+        <v>7284315</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1755,32 +1755,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127148040</v>
+        <v>127148051</v>
       </c>
       <c r="B13" t="n">
-        <v>97333</v>
+        <v>78687</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221941</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>718660</v>
+        <v>718726</v>
       </c>
       <c r="R13" t="n">
-        <v>7284356</v>
+        <v>7284409</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1852,32 +1852,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127148051</v>
+        <v>127148040</v>
       </c>
       <c r="B14" t="n">
-        <v>78687</v>
+        <v>97333</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>221941</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>718726</v>
+        <v>718660</v>
       </c>
       <c r="R14" t="n">
-        <v>7284409</v>
+        <v>7284356</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2046,32 +2046,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127148031</v>
+        <v>127148042</v>
       </c>
       <c r="B16" t="n">
-        <v>79099</v>
+        <v>97333</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>864</v>
+        <v>221941</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>718770</v>
+        <v>718677</v>
       </c>
       <c r="R16" t="n">
-        <v>7284311</v>
+        <v>7284327</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2125,7 +2125,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2144,32 +2143,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127148062</v>
+        <v>127148031</v>
       </c>
       <c r="B17" t="n">
-        <v>92622</v>
+        <v>79099</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>864</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2179,10 +2178,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>718734</v>
+        <v>718770</v>
       </c>
       <c r="R17" t="n">
-        <v>7284278</v>
+        <v>7284311</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2223,6 +2222,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2241,10 +2241,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127148045</v>
+        <v>127148062</v>
       </c>
       <c r="B18" t="n">
-        <v>80151</v>
+        <v>92622</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2252,21 +2252,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6461</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2276,10 +2276,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>718709</v>
+        <v>718734</v>
       </c>
       <c r="R18" t="n">
-        <v>7284346</v>
+        <v>7284278</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2338,10 +2338,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127148042</v>
+        <v>127148045</v>
       </c>
       <c r="B19" t="n">
-        <v>97333</v>
+        <v>80151</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2349,21 +2349,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221941</v>
+        <v>6461</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2373,10 +2373,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>718677</v>
+        <v>718709</v>
       </c>
       <c r="R19" t="n">
-        <v>7284327</v>
+        <v>7284346</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2435,32 +2435,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127148021</v>
+        <v>127148054</v>
       </c>
       <c r="B20" t="n">
-        <v>79638</v>
+        <v>92622</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2470,10 +2470,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>718756</v>
+        <v>718747</v>
       </c>
       <c r="R20" t="n">
-        <v>7284289</v>
+        <v>7284415</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2532,7 +2532,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127148054</v>
+        <v>127148065</v>
       </c>
       <c r="B21" t="n">
         <v>92622</v>
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>718747</v>
+        <v>718669</v>
       </c>
       <c r="R21" t="n">
-        <v>7284415</v>
+        <v>7284342</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2629,32 +2629,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127148065</v>
+        <v>127148021</v>
       </c>
       <c r="B22" t="n">
-        <v>92622</v>
+        <v>79638</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2664,10 +2664,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>718669</v>
+        <v>718756</v>
       </c>
       <c r="R22" t="n">
-        <v>7284342</v>
+        <v>7284289</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -3017,7 +3017,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127148064</v>
+        <v>127148060</v>
       </c>
       <c r="B26" t="n">
         <v>92622</v>
@@ -3052,10 +3052,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>718686</v>
+        <v>718731</v>
       </c>
       <c r="R26" t="n">
-        <v>7284325</v>
+        <v>7284349</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3114,7 +3114,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127148060</v>
+        <v>127148064</v>
       </c>
       <c r="B27" t="n">
         <v>92622</v>
@@ -3149,10 +3149,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>718731</v>
+        <v>718686</v>
       </c>
       <c r="R27" t="n">
-        <v>7284349</v>
+        <v>7284325</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>

--- a/artfynd/A 58862-2024 artfynd.xlsx
+++ b/artfynd/A 58862-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127148032</v>
       </c>
       <c r="B2" t="n">
-        <v>97333</v>
+        <v>97339</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>127148041</v>
       </c>
       <c r="B4" t="n">
-        <v>97333</v>
+        <v>97339</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -970,49 +970,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127148022</v>
+        <v>127148039</v>
       </c>
       <c r="B5" t="n">
-        <v>57663</v>
+        <v>97339</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Grisberget, Pi lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>718730</v>
+        <v>718678</v>
       </c>
       <c r="R5" t="n">
-        <v>7284454</v>
+        <v>7284335</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1045,11 +1041,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska ringhack över stor del av stammen.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1076,45 +1067,49 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127148039</v>
+        <v>127148022</v>
       </c>
       <c r="B6" t="n">
-        <v>97333</v>
+        <v>57663</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Grisberget, Pi lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>718678</v>
+        <v>718730</v>
       </c>
       <c r="R6" t="n">
-        <v>7284335</v>
+        <v>7284454</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1147,6 +1142,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska ringhack över stor del av stammen.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1176,7 +1176,7 @@
         <v>127148059</v>
       </c>
       <c r="B7" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>127148036</v>
       </c>
       <c r="B8" t="n">
-        <v>97333</v>
+        <v>97339</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>127148038</v>
       </c>
       <c r="B9" t="n">
-        <v>97333</v>
+        <v>97339</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>127148033</v>
       </c>
       <c r="B10" t="n">
-        <v>97333</v>
+        <v>97339</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>127148063</v>
       </c>
       <c r="B11" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1658,10 +1658,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127148068</v>
+        <v>127148051</v>
       </c>
       <c r="B12" t="n">
-        <v>78426</v>
+        <v>78687</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1669,21 +1669,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1693,10 +1693,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>718777</v>
+        <v>718726</v>
       </c>
       <c r="R12" t="n">
-        <v>7284375</v>
+        <v>7284409</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1755,10 +1755,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127148051</v>
+        <v>127148068</v>
       </c>
       <c r="B13" t="n">
-        <v>78687</v>
+        <v>78426</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1766,21 +1766,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>718726</v>
+        <v>718777</v>
       </c>
       <c r="R13" t="n">
-        <v>7284409</v>
+        <v>7284375</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1855,7 +1855,7 @@
         <v>127148040</v>
       </c>
       <c r="B14" t="n">
-        <v>97333</v>
+        <v>97339</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2046,32 +2046,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127148042</v>
+        <v>127148031</v>
       </c>
       <c r="B16" t="n">
-        <v>97333</v>
+        <v>79099</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221941</v>
+        <v>864</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>718677</v>
+        <v>718770</v>
       </c>
       <c r="R16" t="n">
-        <v>7284327</v>
+        <v>7284311</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2125,6 +2125,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2143,32 +2144,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127148031</v>
+        <v>127148045</v>
       </c>
       <c r="B17" t="n">
-        <v>79099</v>
+        <v>80151</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>864</v>
+        <v>6461</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2178,10 +2179,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>718770</v>
+        <v>718709</v>
       </c>
       <c r="R17" t="n">
-        <v>7284311</v>
+        <v>7284346</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2222,7 +2223,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2244,7 +2244,7 @@
         <v>127148062</v>
       </c>
       <c r="B18" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2338,10 +2338,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127148045</v>
+        <v>127148042</v>
       </c>
       <c r="B19" t="n">
-        <v>80151</v>
+        <v>97339</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2349,21 +2349,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6461</v>
+        <v>221941</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2373,10 +2373,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>718709</v>
+        <v>718677</v>
       </c>
       <c r="R19" t="n">
-        <v>7284346</v>
+        <v>7284327</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2438,7 +2438,7 @@
         <v>127148054</v>
       </c>
       <c r="B20" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>127148065</v>
       </c>
       <c r="B21" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         <v>127148034</v>
       </c>
       <c r="B23" t="n">
-        <v>97333</v>
+        <v>97339</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>127148058</v>
       </c>
       <c r="B24" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>127148057</v>
       </c>
       <c r="B25" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>127148060</v>
       </c>
       <c r="B26" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
         <v>127148064</v>
       </c>
       <c r="B27" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
         <v>127148056</v>
       </c>
       <c r="B28" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>127148055</v>
       </c>
       <c r="B29" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3405,10 +3405,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127148061</v>
+        <v>127148043</v>
       </c>
       <c r="B30" t="n">
-        <v>92622</v>
+        <v>97339</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3416,21 +3416,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3440,10 +3440,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>718771</v>
+        <v>718667</v>
       </c>
       <c r="R30" t="n">
-        <v>7284306</v>
+        <v>7284313</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3502,32 +3502,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127148020</v>
+        <v>127148035</v>
       </c>
       <c r="B31" t="n">
-        <v>79638</v>
+        <v>97339</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6453</v>
+        <v>221941</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3537,10 +3537,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>718765</v>
+        <v>718776</v>
       </c>
       <c r="R31" t="n">
-        <v>7284389</v>
+        <v>7284309</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3599,10 +3599,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127148043</v>
+        <v>127148061</v>
       </c>
       <c r="B32" t="n">
-        <v>97333</v>
+        <v>92628</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3610,21 +3610,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3634,10 +3634,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>718667</v>
+        <v>718771</v>
       </c>
       <c r="R32" t="n">
-        <v>7284313</v>
+        <v>7284306</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3696,32 +3696,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127148035</v>
+        <v>127148020</v>
       </c>
       <c r="B33" t="n">
-        <v>97333</v>
+        <v>79638</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221941</v>
+        <v>6453</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3731,10 +3731,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>718776</v>
+        <v>718765</v>
       </c>
       <c r="R33" t="n">
-        <v>7284309</v>
+        <v>7284389</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>

--- a/artfynd/A 58862-2024 artfynd.xlsx
+++ b/artfynd/A 58862-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127148032</v>
       </c>
       <c r="B2" t="n">
-        <v>97339</v>
+        <v>97342</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127148067</v>
       </c>
       <c r="B3" t="n">
-        <v>79099</v>
+        <v>79102</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>127148041</v>
       </c>
       <c r="B4" t="n">
-        <v>97339</v>
+        <v>97342</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -970,45 +970,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127148039</v>
+        <v>127148022</v>
       </c>
       <c r="B5" t="n">
-        <v>97339</v>
+        <v>57666</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221941</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Grisberget, Pi lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>718678</v>
+        <v>718730</v>
       </c>
       <c r="R5" t="n">
-        <v>7284335</v>
+        <v>7284454</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1041,6 +1045,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska ringhack över stor del av stammen.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1067,49 +1076,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127148022</v>
+        <v>127148039</v>
       </c>
       <c r="B6" t="n">
-        <v>57663</v>
+        <v>97342</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>221941</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Grisberget, Pi lm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>718730</v>
+        <v>718678</v>
       </c>
       <c r="R6" t="n">
-        <v>7284454</v>
+        <v>7284335</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1142,11 +1147,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska ringhack över stor del av stammen.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1176,7 +1176,7 @@
         <v>127148059</v>
       </c>
       <c r="B7" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>127148036</v>
       </c>
       <c r="B8" t="n">
-        <v>97339</v>
+        <v>97342</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>127148038</v>
       </c>
       <c r="B9" t="n">
-        <v>97339</v>
+        <v>97342</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>127148033</v>
       </c>
       <c r="B10" t="n">
-        <v>97339</v>
+        <v>97342</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>127148063</v>
       </c>
       <c r="B11" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>127148051</v>
       </c>
       <c r="B12" t="n">
-        <v>78687</v>
+        <v>78690</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         <v>127148068</v>
       </c>
       <c r="B13" t="n">
-        <v>78426</v>
+        <v>78429</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1855,7 +1855,7 @@
         <v>127148040</v>
       </c>
       <c r="B14" t="n">
-        <v>97339</v>
+        <v>97342</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         <v>127148046</v>
       </c>
       <c r="B15" t="n">
-        <v>78779</v>
+        <v>78782</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2046,32 +2046,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127148031</v>
+        <v>127148042</v>
       </c>
       <c r="B16" t="n">
-        <v>79099</v>
+        <v>97342</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>864</v>
+        <v>221941</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>718770</v>
+        <v>718677</v>
       </c>
       <c r="R16" t="n">
-        <v>7284311</v>
+        <v>7284327</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2125,7 +2125,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2144,32 +2143,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127148045</v>
+        <v>127148031</v>
       </c>
       <c r="B17" t="n">
-        <v>80151</v>
+        <v>79102</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6461</v>
+        <v>864</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2179,10 +2178,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>718709</v>
+        <v>718770</v>
       </c>
       <c r="R17" t="n">
-        <v>7284346</v>
+        <v>7284311</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2223,6 +2222,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2241,10 +2241,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127148062</v>
+        <v>127148045</v>
       </c>
       <c r="B18" t="n">
-        <v>92628</v>
+        <v>80154</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2252,21 +2252,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>6461</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2276,10 +2276,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>718734</v>
+        <v>718709</v>
       </c>
       <c r="R18" t="n">
-        <v>7284278</v>
+        <v>7284346</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2338,10 +2338,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127148042</v>
+        <v>127148062</v>
       </c>
       <c r="B19" t="n">
-        <v>97339</v>
+        <v>92631</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2349,21 +2349,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2373,10 +2373,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>718677</v>
+        <v>718734</v>
       </c>
       <c r="R19" t="n">
-        <v>7284327</v>
+        <v>7284278</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2435,10 +2435,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127148054</v>
+        <v>127148034</v>
       </c>
       <c r="B20" t="n">
-        <v>92628</v>
+        <v>97342</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2446,21 +2446,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2470,10 +2470,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>718747</v>
+        <v>718761</v>
       </c>
       <c r="R20" t="n">
-        <v>7284415</v>
+        <v>7284321</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2532,10 +2532,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127148065</v>
+        <v>127148054</v>
       </c>
       <c r="B21" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>718669</v>
+        <v>718747</v>
       </c>
       <c r="R21" t="n">
-        <v>7284342</v>
+        <v>7284415</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2629,32 +2629,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127148021</v>
+        <v>127148065</v>
       </c>
       <c r="B22" t="n">
-        <v>79638</v>
+        <v>92631</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2664,10 +2664,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>718756</v>
+        <v>718669</v>
       </c>
       <c r="R22" t="n">
-        <v>7284289</v>
+        <v>7284342</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2726,32 +2726,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127148034</v>
+        <v>127148021</v>
       </c>
       <c r="B23" t="n">
-        <v>97339</v>
+        <v>79641</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221941</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2761,10 +2761,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>718761</v>
+        <v>718756</v>
       </c>
       <c r="R23" t="n">
-        <v>7284321</v>
+        <v>7284289</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2826,7 +2826,7 @@
         <v>127148058</v>
       </c>
       <c r="B24" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>127148057</v>
       </c>
       <c r="B25" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>127148060</v>
       </c>
       <c r="B26" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
         <v>127148064</v>
       </c>
       <c r="B27" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
         <v>127148056</v>
       </c>
       <c r="B28" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>127148055</v>
       </c>
       <c r="B29" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3405,32 +3405,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127148043</v>
+        <v>127148020</v>
       </c>
       <c r="B30" t="n">
-        <v>97339</v>
+        <v>79641</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221941</v>
+        <v>6453</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3440,10 +3440,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>718667</v>
+        <v>718765</v>
       </c>
       <c r="R30" t="n">
-        <v>7284313</v>
+        <v>7284389</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3502,10 +3502,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127148035</v>
+        <v>127148061</v>
       </c>
       <c r="B31" t="n">
-        <v>97339</v>
+        <v>92631</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3513,21 +3513,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3537,10 +3537,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>718776</v>
+        <v>718771</v>
       </c>
       <c r="R31" t="n">
-        <v>7284309</v>
+        <v>7284306</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3599,10 +3599,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127148061</v>
+        <v>127148043</v>
       </c>
       <c r="B32" t="n">
-        <v>92628</v>
+        <v>97342</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3610,21 +3610,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3634,10 +3634,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>718771</v>
+        <v>718667</v>
       </c>
       <c r="R32" t="n">
-        <v>7284306</v>
+        <v>7284313</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3696,32 +3696,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127148020</v>
+        <v>127148035</v>
       </c>
       <c r="B33" t="n">
-        <v>79638</v>
+        <v>97342</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6453</v>
+        <v>221941</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3731,10 +3731,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>718765</v>
+        <v>718776</v>
       </c>
       <c r="R33" t="n">
-        <v>7284389</v>
+        <v>7284309</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3796,7 +3796,7 @@
         <v>127148030</v>
       </c>
       <c r="B34" t="n">
-        <v>57660</v>
+        <v>57663</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 58862-2024 artfynd.xlsx
+++ b/artfynd/A 58862-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127148032</v>
       </c>
       <c r="B2" t="n">
-        <v>97342</v>
+        <v>97350</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127148067</v>
       </c>
       <c r="B3" t="n">
-        <v>79102</v>
+        <v>79108</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>127148041</v>
       </c>
       <c r="B4" t="n">
-        <v>97342</v>
+        <v>97350</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>127148022</v>
       </c>
       <c r="B5" t="n">
-        <v>57666</v>
+        <v>57672</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>127148039</v>
       </c>
       <c r="B6" t="n">
-        <v>97342</v>
+        <v>97350</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,10 +1173,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127148059</v>
+        <v>127148036</v>
       </c>
       <c r="B7" t="n">
-        <v>92631</v>
+        <v>97350</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1184,21 +1184,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1208,10 +1208,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>718785</v>
+        <v>718709</v>
       </c>
       <c r="R7" t="n">
-        <v>7284347</v>
+        <v>7284315</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1270,10 +1270,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127148036</v>
+        <v>127148059</v>
       </c>
       <c r="B8" t="n">
-        <v>97342</v>
+        <v>92639</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1281,21 +1281,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1305,10 +1305,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>718709</v>
+        <v>718785</v>
       </c>
       <c r="R8" t="n">
-        <v>7284315</v>
+        <v>7284347</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1370,7 +1370,7 @@
         <v>127148038</v>
       </c>
       <c r="B9" t="n">
-        <v>97342</v>
+        <v>97350</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>127148033</v>
       </c>
       <c r="B10" t="n">
-        <v>97342</v>
+        <v>97350</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>127148063</v>
       </c>
       <c r="B11" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1658,10 +1658,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127148051</v>
+        <v>127148068</v>
       </c>
       <c r="B12" t="n">
-        <v>78690</v>
+        <v>78435</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1669,21 +1669,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1693,10 +1693,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>718726</v>
+        <v>718777</v>
       </c>
       <c r="R12" t="n">
-        <v>7284409</v>
+        <v>7284375</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1755,32 +1755,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127148068</v>
+        <v>127148040</v>
       </c>
       <c r="B13" t="n">
-        <v>78429</v>
+        <v>97350</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6437</v>
+        <v>221941</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>718777</v>
+        <v>718660</v>
       </c>
       <c r="R13" t="n">
-        <v>7284375</v>
+        <v>7284356</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1852,32 +1852,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127148040</v>
+        <v>127148051</v>
       </c>
       <c r="B14" t="n">
-        <v>97342</v>
+        <v>78696</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221941</v>
+        <v>353</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>718660</v>
+        <v>718726</v>
       </c>
       <c r="R14" t="n">
-        <v>7284356</v>
+        <v>7284409</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1952,7 +1952,7 @@
         <v>127148046</v>
       </c>
       <c r="B15" t="n">
-        <v>78782</v>
+        <v>78788</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2046,10 +2046,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127148042</v>
+        <v>127148045</v>
       </c>
       <c r="B16" t="n">
-        <v>97342</v>
+        <v>80160</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2057,21 +2057,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221941</v>
+        <v>6461</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>718677</v>
+        <v>718709</v>
       </c>
       <c r="R16" t="n">
-        <v>7284327</v>
+        <v>7284346</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2143,32 +2143,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127148031</v>
+        <v>127148062</v>
       </c>
       <c r="B17" t="n">
-        <v>79102</v>
+        <v>92639</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>864</v>
+        <v>4364</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>718770</v>
+        <v>718734</v>
       </c>
       <c r="R17" t="n">
-        <v>7284311</v>
+        <v>7284278</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2222,7 +2222,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2241,32 +2240,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127148045</v>
+        <v>127148031</v>
       </c>
       <c r="B18" t="n">
-        <v>80154</v>
+        <v>79108</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6461</v>
+        <v>864</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2276,10 +2275,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>718709</v>
+        <v>718770</v>
       </c>
       <c r="R18" t="n">
-        <v>7284346</v>
+        <v>7284311</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2320,6 +2319,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2338,10 +2338,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127148062</v>
+        <v>127148042</v>
       </c>
       <c r="B19" t="n">
-        <v>92631</v>
+        <v>97350</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2349,21 +2349,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2373,10 +2373,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>718734</v>
+        <v>718677</v>
       </c>
       <c r="R19" t="n">
-        <v>7284278</v>
+        <v>7284327</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2435,10 +2435,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127148034</v>
+        <v>127148054</v>
       </c>
       <c r="B20" t="n">
-        <v>97342</v>
+        <v>92639</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2446,21 +2446,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2470,10 +2470,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>718761</v>
+        <v>718747</v>
       </c>
       <c r="R20" t="n">
-        <v>7284321</v>
+        <v>7284415</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2532,10 +2532,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127148054</v>
+        <v>127148065</v>
       </c>
       <c r="B21" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2567,10 +2567,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>718747</v>
+        <v>718669</v>
       </c>
       <c r="R21" t="n">
-        <v>7284415</v>
+        <v>7284342</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2629,32 +2629,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127148065</v>
+        <v>127148021</v>
       </c>
       <c r="B22" t="n">
-        <v>92631</v>
+        <v>79647</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2664,10 +2664,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>718669</v>
+        <v>718756</v>
       </c>
       <c r="R22" t="n">
-        <v>7284342</v>
+        <v>7284289</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2726,32 +2726,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127148021</v>
+        <v>127148034</v>
       </c>
       <c r="B23" t="n">
-        <v>79641</v>
+        <v>97350</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>221941</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2761,10 +2761,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>718756</v>
+        <v>718761</v>
       </c>
       <c r="R23" t="n">
-        <v>7284289</v>
+        <v>7284321</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2826,7 +2826,7 @@
         <v>127148058</v>
       </c>
       <c r="B24" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>127148057</v>
       </c>
       <c r="B25" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>127148060</v>
       </c>
       <c r="B26" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
         <v>127148064</v>
       </c>
       <c r="B27" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
         <v>127148056</v>
       </c>
       <c r="B28" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>127148055</v>
       </c>
       <c r="B29" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3408,7 +3408,7 @@
         <v>127148020</v>
       </c>
       <c r="B30" t="n">
-        <v>79641</v>
+        <v>79647</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>127148061</v>
       </c>
       <c r="B31" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3602,7 +3602,7 @@
         <v>127148043</v>
       </c>
       <c r="B32" t="n">
-        <v>97342</v>
+        <v>97350</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>127148035</v>
       </c>
       <c r="B33" t="n">
-        <v>97342</v>
+        <v>97350</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3796,7 +3796,7 @@
         <v>127148030</v>
       </c>
       <c r="B34" t="n">
-        <v>57663</v>
+        <v>57669</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 58862-2024 artfynd.xlsx
+++ b/artfynd/A 58862-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127148032</v>
       </c>
       <c r="B2" t="n">
-        <v>97350</v>
+        <v>97351</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>127148041</v>
       </c>
       <c r="B4" t="n">
-        <v>97350</v>
+        <v>97351</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>127148039</v>
       </c>
       <c r="B6" t="n">
-        <v>97350</v>
+        <v>97351</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>127148036</v>
       </c>
       <c r="B7" t="n">
-        <v>97350</v>
+        <v>97351</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>127148059</v>
       </c>
       <c r="B8" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>127148038</v>
       </c>
       <c r="B9" t="n">
-        <v>97350</v>
+        <v>97351</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>127148033</v>
       </c>
       <c r="B10" t="n">
-        <v>97350</v>
+        <v>97351</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>127148063</v>
       </c>
       <c r="B11" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1755,32 +1755,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127148040</v>
+        <v>127148051</v>
       </c>
       <c r="B13" t="n">
-        <v>97350</v>
+        <v>78696</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221941</v>
+        <v>353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>718660</v>
+        <v>718726</v>
       </c>
       <c r="R13" t="n">
-        <v>7284356</v>
+        <v>7284409</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1852,32 +1852,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127148051</v>
+        <v>127148040</v>
       </c>
       <c r="B14" t="n">
-        <v>78696</v>
+        <v>97351</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>353</v>
+        <v>221941</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1887,10 +1887,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>718726</v>
+        <v>718660</v>
       </c>
       <c r="R14" t="n">
-        <v>7284409</v>
+        <v>7284356</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2046,10 +2046,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127148045</v>
+        <v>127148042</v>
       </c>
       <c r="B16" t="n">
-        <v>80160</v>
+        <v>97351</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2057,21 +2057,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6461</v>
+        <v>221941</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>718709</v>
+        <v>718677</v>
       </c>
       <c r="R16" t="n">
-        <v>7284346</v>
+        <v>7284327</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2143,10 +2143,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127148062</v>
+        <v>127148045</v>
       </c>
       <c r="B17" t="n">
-        <v>92639</v>
+        <v>80160</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2154,21 +2154,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>4364</v>
+        <v>6461</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>718734</v>
+        <v>718709</v>
       </c>
       <c r="R17" t="n">
-        <v>7284278</v>
+        <v>7284346</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2240,32 +2240,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127148031</v>
+        <v>127148062</v>
       </c>
       <c r="B18" t="n">
-        <v>79108</v>
+        <v>92640</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>864</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2275,10 +2275,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>718770</v>
+        <v>718734</v>
       </c>
       <c r="R18" t="n">
-        <v>7284311</v>
+        <v>7284278</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2319,7 +2319,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2338,32 +2337,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127148042</v>
+        <v>127148031</v>
       </c>
       <c r="B19" t="n">
-        <v>97350</v>
+        <v>79108</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221941</v>
+        <v>864</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2373,10 +2372,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>718677</v>
+        <v>718770</v>
       </c>
       <c r="R19" t="n">
-        <v>7284327</v>
+        <v>7284311</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2417,6 +2416,7 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2438,7 +2438,7 @@
         <v>127148054</v>
       </c>
       <c r="B20" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>127148065</v>
       </c>
       <c r="B21" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         <v>127148034</v>
       </c>
       <c r="B23" t="n">
-        <v>97350</v>
+        <v>97351</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>127148058</v>
       </c>
       <c r="B24" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>127148057</v>
       </c>
       <c r="B25" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
         <v>127148060</v>
       </c>
       <c r="B26" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3117,7 +3117,7 @@
         <v>127148064</v>
       </c>
       <c r="B27" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3214,7 +3214,7 @@
         <v>127148056</v>
       </c>
       <c r="B28" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>127148055</v>
       </c>
       <c r="B29" t="n">
-        <v>92639</v>
+        <v>92640</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3405,32 +3405,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127148020</v>
+        <v>127148043</v>
       </c>
       <c r="B30" t="n">
-        <v>79647</v>
+        <v>97351</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>221941</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3440,10 +3440,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>718765</v>
+        <v>718667</v>
       </c>
       <c r="R30" t="n">
-        <v>7284389</v>
+        <v>7284313</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3502,10 +3502,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127148061</v>
+        <v>127148035</v>
       </c>
       <c r="B31" t="n">
-        <v>92639</v>
+        <v>97351</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3513,21 +3513,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3537,10 +3537,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>718771</v>
+        <v>718776</v>
       </c>
       <c r="R31" t="n">
-        <v>7284306</v>
+        <v>7284309</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3599,32 +3599,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127148043</v>
+        <v>127148020</v>
       </c>
       <c r="B32" t="n">
-        <v>97350</v>
+        <v>79647</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221941</v>
+        <v>6453</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3634,10 +3634,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>718667</v>
+        <v>718765</v>
       </c>
       <c r="R32" t="n">
-        <v>7284313</v>
+        <v>7284389</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3696,10 +3696,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127148035</v>
+        <v>127148061</v>
       </c>
       <c r="B33" t="n">
-        <v>97350</v>
+        <v>92640</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3707,21 +3707,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3731,10 +3731,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>718776</v>
+        <v>718771</v>
       </c>
       <c r="R33" t="n">
-        <v>7284309</v>
+        <v>7284306</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>

--- a/artfynd/A 58862-2024 artfynd.xlsx
+++ b/artfynd/A 58862-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127148032</v>
       </c>
       <c r="B2" t="n">
-        <v>97351</v>
+        <v>97320</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>127148067</v>
       </c>
       <c r="B3" t="n">
-        <v>79108</v>
+        <v>79090</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -876,7 +876,7 @@
         <v>127148041</v>
       </c>
       <c r="B4" t="n">
-        <v>97351</v>
+        <v>97320</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>127148022</v>
       </c>
       <c r="B5" t="n">
-        <v>57672</v>
+        <v>57657</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1079,7 +1079,7 @@
         <v>127148039</v>
       </c>
       <c r="B6" t="n">
-        <v>97351</v>
+        <v>97320</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1176,7 +1176,7 @@
         <v>127148036</v>
       </c>
       <c r="B7" t="n">
-        <v>97351</v>
+        <v>97320</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
         <v>127148059</v>
       </c>
       <c r="B8" t="n">
-        <v>92640</v>
+        <v>92609</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
         <v>127148038</v>
       </c>
       <c r="B9" t="n">
-        <v>97351</v>
+        <v>97320</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>127148033</v>
       </c>
       <c r="B10" t="n">
-        <v>97351</v>
+        <v>97320</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1564,7 +1564,7 @@
         <v>127148063</v>
       </c>
       <c r="B11" t="n">
-        <v>92640</v>
+        <v>92609</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1658,10 +1658,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127148068</v>
+        <v>127148051</v>
       </c>
       <c r="B12" t="n">
-        <v>78435</v>
+        <v>78678</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1669,21 +1669,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6437</v>
+        <v>353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1693,10 +1693,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>718777</v>
+        <v>718726</v>
       </c>
       <c r="R12" t="n">
-        <v>7284375</v>
+        <v>7284409</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1755,10 +1755,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127148051</v>
+        <v>127148068</v>
       </c>
       <c r="B13" t="n">
-        <v>78696</v>
+        <v>78417</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1766,21 +1766,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>6437</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1790,10 +1790,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>718726</v>
+        <v>718777</v>
       </c>
       <c r="R13" t="n">
-        <v>7284409</v>
+        <v>7284375</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1855,7 +1855,7 @@
         <v>127148040</v>
       </c>
       <c r="B14" t="n">
-        <v>97351</v>
+        <v>97320</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1952,7 +1952,7 @@
         <v>127148046</v>
       </c>
       <c r="B15" t="n">
-        <v>78788</v>
+        <v>78770</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2046,10 +2046,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127148042</v>
+        <v>127148062</v>
       </c>
       <c r="B16" t="n">
-        <v>97351</v>
+        <v>92609</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2057,21 +2057,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>718677</v>
+        <v>718734</v>
       </c>
       <c r="R16" t="n">
-        <v>7284327</v>
+        <v>7284278</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2143,32 +2143,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127148045</v>
+        <v>127148031</v>
       </c>
       <c r="B17" t="n">
-        <v>80160</v>
+        <v>79090</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6461</v>
+        <v>864</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2178,10 +2178,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>718709</v>
+        <v>718770</v>
       </c>
       <c r="R17" t="n">
-        <v>7284346</v>
+        <v>7284311</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2222,6 +2222,7 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2240,10 +2241,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127148062</v>
+        <v>127148045</v>
       </c>
       <c r="B18" t="n">
-        <v>92640</v>
+        <v>80142</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2251,21 +2252,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>6461</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2275,10 +2276,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>718734</v>
+        <v>718709</v>
       </c>
       <c r="R18" t="n">
-        <v>7284278</v>
+        <v>7284346</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2337,32 +2338,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127148031</v>
+        <v>127148042</v>
       </c>
       <c r="B19" t="n">
-        <v>79108</v>
+        <v>97320</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>864</v>
+        <v>221941</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2372,10 +2373,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>718770</v>
+        <v>718677</v>
       </c>
       <c r="R19" t="n">
-        <v>7284311</v>
+        <v>7284327</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2416,7 +2417,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2438,7 +2438,7 @@
         <v>127148054</v>
       </c>
       <c r="B20" t="n">
-        <v>92640</v>
+        <v>92609</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2535,7 +2535,7 @@
         <v>127148065</v>
       </c>
       <c r="B21" t="n">
-        <v>92640</v>
+        <v>92609</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2629,32 +2629,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127148021</v>
+        <v>127148034</v>
       </c>
       <c r="B22" t="n">
-        <v>79647</v>
+        <v>97320</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>221941</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2664,10 +2664,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>718756</v>
+        <v>718761</v>
       </c>
       <c r="R22" t="n">
-        <v>7284289</v>
+        <v>7284321</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2726,32 +2726,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127148034</v>
+        <v>127148021</v>
       </c>
       <c r="B23" t="n">
-        <v>97351</v>
+        <v>79629</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221941</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2761,10 +2761,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>718761</v>
+        <v>718756</v>
       </c>
       <c r="R23" t="n">
-        <v>7284321</v>
+        <v>7284289</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2826,7 +2826,7 @@
         <v>127148058</v>
       </c>
       <c r="B24" t="n">
-        <v>92640</v>
+        <v>92609</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>127148057</v>
       </c>
       <c r="B25" t="n">
-        <v>92640</v>
+        <v>92609</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3017,10 +3017,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127148060</v>
+        <v>127148064</v>
       </c>
       <c r="B26" t="n">
-        <v>92640</v>
+        <v>92609</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3052,10 +3052,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>718731</v>
+        <v>718686</v>
       </c>
       <c r="R26" t="n">
-        <v>7284349</v>
+        <v>7284325</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3114,10 +3114,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127148064</v>
+        <v>127148060</v>
       </c>
       <c r="B27" t="n">
-        <v>92640</v>
+        <v>92609</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3149,10 +3149,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>718686</v>
+        <v>718731</v>
       </c>
       <c r="R27" t="n">
-        <v>7284325</v>
+        <v>7284349</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3214,7 +3214,7 @@
         <v>127148056</v>
       </c>
       <c r="B28" t="n">
-        <v>92640</v>
+        <v>92609</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3311,7 +3311,7 @@
         <v>127148055</v>
       </c>
       <c r="B29" t="n">
-        <v>92640</v>
+        <v>92609</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3405,10 +3405,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127148043</v>
+        <v>127148061</v>
       </c>
       <c r="B30" t="n">
-        <v>97351</v>
+        <v>92609</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3416,21 +3416,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3440,10 +3440,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>718667</v>
+        <v>718771</v>
       </c>
       <c r="R30" t="n">
-        <v>7284313</v>
+        <v>7284306</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3502,32 +3502,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127148035</v>
+        <v>127148020</v>
       </c>
       <c r="B31" t="n">
-        <v>97351</v>
+        <v>79629</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221941</v>
+        <v>6453</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3537,10 +3537,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>718776</v>
+        <v>718765</v>
       </c>
       <c r="R31" t="n">
-        <v>7284309</v>
+        <v>7284389</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3599,32 +3599,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127148020</v>
+        <v>127148043</v>
       </c>
       <c r="B32" t="n">
-        <v>79647</v>
+        <v>97320</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>221941</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3634,10 +3634,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>718765</v>
+        <v>718667</v>
       </c>
       <c r="R32" t="n">
-        <v>7284389</v>
+        <v>7284313</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3696,10 +3696,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127148061</v>
+        <v>127148035</v>
       </c>
       <c r="B33" t="n">
-        <v>92640</v>
+        <v>97320</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3707,21 +3707,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3731,10 +3731,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>718771</v>
+        <v>718776</v>
       </c>
       <c r="R33" t="n">
-        <v>7284306</v>
+        <v>7284309</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3796,7 +3796,7 @@
         <v>127148030</v>
       </c>
       <c r="B34" t="n">
-        <v>57669</v>
+        <v>57654</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>

--- a/artfynd/A 58862-2024 artfynd.xlsx
+++ b/artfynd/A 58862-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY34"/>
+  <dimension ref="A1:AY38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>127148032</v>
+        <v>127148051</v>
       </c>
       <c r="B2" t="n">
-        <v>97351</v>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221941</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>718718</v>
+        <v>718726</v>
       </c>
       <c r="R2" t="n">
-        <v>7284349</v>
+        <v>7284409</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127148067</v>
+        <v>127148031</v>
       </c>
       <c r="B3" t="n">
-        <v>79108</v>
+        <v>79406</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -801,19 +801,16 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Grisberget, Pi lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>718693</v>
+        <v>718770</v>
       </c>
       <c r="R3" t="n">
-        <v>7284396</v>
+        <v>7284311</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -873,45 +870,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>127148041</v>
+        <v>127148067</v>
       </c>
       <c r="B4" t="n">
-        <v>97351</v>
+        <v>79406</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221941</v>
+        <v>864</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lynge) Ahti</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Grisberget, Pi lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>718660</v>
+        <v>718693</v>
       </c>
       <c r="R4" t="n">
-        <v>7284340</v>
+        <v>7284396</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -952,6 +952,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -970,10 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127148022</v>
+        <v>127148054</v>
       </c>
       <c r="B5" t="n">
-        <v>57672</v>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -981,38 +982,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Grisberget, Pi lm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>718730</v>
+        <v>718747</v>
       </c>
       <c r="R5" t="n">
-        <v>7284454</v>
+        <v>7284415</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1045,11 +1042,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-08-03</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska ringhack över stor del av stammen.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1076,32 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127148039</v>
+        <v>127148055</v>
       </c>
       <c r="B6" t="n">
-        <v>97351</v>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1111,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>718678</v>
+        <v>718732</v>
       </c>
       <c r="R6" t="n">
-        <v>7284335</v>
+        <v>7284447</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1173,32 +1165,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127148036</v>
+        <v>127148056</v>
       </c>
       <c r="B7" t="n">
-        <v>97351</v>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1208,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>718709</v>
+        <v>718730</v>
       </c>
       <c r="R7" t="n">
-        <v>7284315</v>
+        <v>7284454</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1270,14 +1262,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127148059</v>
+        <v>127148057</v>
       </c>
       <c r="B8" t="n">
-        <v>92640</v>
+        <v>93197</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1305,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>718785</v>
+        <v>718800</v>
       </c>
       <c r="R8" t="n">
-        <v>7284347</v>
+        <v>7284346</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1367,32 +1359,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127148038</v>
+        <v>127148058</v>
       </c>
       <c r="B9" t="n">
-        <v>97351</v>
+        <v>93197</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1402,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>718694</v>
+        <v>718815</v>
       </c>
       <c r="R9" t="n">
-        <v>7284325</v>
+        <v>7284323</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1464,32 +1456,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>127148033</v>
+        <v>127148059</v>
       </c>
       <c r="B10" t="n">
-        <v>97351</v>
+        <v>93197</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1499,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>718773</v>
+        <v>718785</v>
       </c>
       <c r="R10" t="n">
-        <v>7284302</v>
+        <v>7284347</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1561,14 +1553,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>127148063</v>
+        <v>127148060</v>
       </c>
       <c r="B11" t="n">
-        <v>92640</v>
+        <v>93197</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1596,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>718729</v>
+        <v>718731</v>
       </c>
       <c r="R11" t="n">
-        <v>7284302</v>
+        <v>7284349</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1658,10 +1650,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>127148068</v>
+        <v>127148061</v>
       </c>
       <c r="B12" t="n">
-        <v>78435</v>
+        <v>93197</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1669,21 +1661,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6437</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1693,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>718777</v>
+        <v>718771</v>
       </c>
       <c r="R12" t="n">
-        <v>7284375</v>
+        <v>7284306</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1755,10 +1747,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>127148051</v>
+        <v>127148062</v>
       </c>
       <c r="B13" t="n">
-        <v>78696</v>
+        <v>93197</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1766,21 +1758,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1790,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>718726</v>
+        <v>718734</v>
       </c>
       <c r="R13" t="n">
-        <v>7284409</v>
+        <v>7284278</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1852,32 +1844,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>127148040</v>
+        <v>127148063</v>
       </c>
       <c r="B14" t="n">
-        <v>97351</v>
+        <v>93197</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1887,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>718660</v>
+        <v>718729</v>
       </c>
       <c r="R14" t="n">
-        <v>7284356</v>
+        <v>7284302</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -1949,10 +1941,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>127148046</v>
+        <v>127148064</v>
       </c>
       <c r="B15" t="n">
-        <v>78788</v>
+        <v>93197</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1960,21 +1952,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1984,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>718742</v>
+        <v>718686</v>
       </c>
       <c r="R15" t="n">
-        <v>7284376</v>
+        <v>7284325</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2046,32 +2038,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>127148042</v>
+        <v>127148065</v>
       </c>
       <c r="B16" t="n">
-        <v>97351</v>
+        <v>93197</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221941</v>
+        <v>4364</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2081,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>718677</v>
+        <v>718669</v>
       </c>
       <c r="R16" t="n">
-        <v>7284327</v>
+        <v>7284342</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2143,32 +2135,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>127148045</v>
+        <v>127148068</v>
       </c>
       <c r="B17" t="n">
-        <v>80160</v>
+        <v>78730</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6461</v>
+        <v>6437</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2178,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>718709</v>
+        <v>718777</v>
       </c>
       <c r="R17" t="n">
-        <v>7284346</v>
+        <v>7284375</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2240,32 +2232,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>127148062</v>
+        <v>127148020</v>
       </c>
       <c r="B18" t="n">
-        <v>92640</v>
+        <v>79946</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2275,10 +2267,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>718734</v>
+        <v>718765</v>
       </c>
       <c r="R18" t="n">
-        <v>7284278</v>
+        <v>7284389</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2337,10 +2329,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>127148031</v>
+        <v>127148021</v>
       </c>
       <c r="B19" t="n">
-        <v>79108</v>
+        <v>79946</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2348,21 +2340,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>864</v>
+        <v>6453</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2372,10 +2364,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>718770</v>
+        <v>718756</v>
       </c>
       <c r="R19" t="n">
-        <v>7284311</v>
+        <v>7284289</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2416,7 +2408,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2435,10 +2426,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>127148054</v>
+        <v>127148045</v>
       </c>
       <c r="B20" t="n">
-        <v>92640</v>
+        <v>80460</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2446,21 +2437,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>4364</v>
+        <v>6461</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2470,10 +2461,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>718747</v>
+        <v>718709</v>
       </c>
       <c r="R20" t="n">
-        <v>7284415</v>
+        <v>7284346</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2532,10 +2523,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>127148065</v>
+        <v>127148030</v>
       </c>
       <c r="B21" t="n">
-        <v>92640</v>
+        <v>57950</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2543,21 +2534,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2567,10 +2558,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>718669</v>
+        <v>718687</v>
       </c>
       <c r="R21" t="n">
-        <v>7284342</v>
+        <v>7284276</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2629,10 +2620,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>127148021</v>
+        <v>127148022</v>
       </c>
       <c r="B22" t="n">
-        <v>79647</v>
+        <v>57953</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2640,34 +2631,38 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
           <t>Grisberget, Pi lm</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>718756</v>
+        <v>718730</v>
       </c>
       <c r="R22" t="n">
-        <v>7284289</v>
+        <v>7284454</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2700,6 +2695,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Färska ringhack över stor del av stammen.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2726,10 +2726,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>127148034</v>
+        <v>127148044</v>
       </c>
       <c r="B23" t="n">
-        <v>97351</v>
+        <v>57144</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2737,21 +2737,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221941</v>
+        <v>102613</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2761,10 +2761,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>718761</v>
+        <v>718714</v>
       </c>
       <c r="R23" t="n">
-        <v>7284321</v>
+        <v>7284241</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -2823,10 +2823,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>127148058</v>
+        <v>127148032</v>
       </c>
       <c r="B24" t="n">
-        <v>92640</v>
+        <v>97989</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2834,21 +2834,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2858,10 +2858,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>718815</v>
+        <v>718718</v>
       </c>
       <c r="R24" t="n">
-        <v>7284323</v>
+        <v>7284349</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -2920,10 +2920,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>127148057</v>
+        <v>127148033</v>
       </c>
       <c r="B25" t="n">
-        <v>92640</v>
+        <v>97989</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2931,21 +2931,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2955,10 +2955,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>718800</v>
+        <v>718773</v>
       </c>
       <c r="R25" t="n">
-        <v>7284346</v>
+        <v>7284302</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3017,10 +3017,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>127148060</v>
+        <v>127148034</v>
       </c>
       <c r="B26" t="n">
-        <v>92640</v>
+        <v>97989</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3028,21 +3028,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3052,10 +3052,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>718731</v>
+        <v>718761</v>
       </c>
       <c r="R26" t="n">
-        <v>7284349</v>
+        <v>7284321</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3114,10 +3114,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>127148064</v>
+        <v>127148035</v>
       </c>
       <c r="B27" t="n">
-        <v>92640</v>
+        <v>97989</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3125,21 +3125,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3149,10 +3149,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>718686</v>
+        <v>718776</v>
       </c>
       <c r="R27" t="n">
-        <v>7284325</v>
+        <v>7284309</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3211,10 +3211,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>127148056</v>
+        <v>127148036</v>
       </c>
       <c r="B28" t="n">
-        <v>92640</v>
+        <v>97989</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3222,21 +3222,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3246,10 +3246,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>718730</v>
+        <v>718709</v>
       </c>
       <c r="R28" t="n">
-        <v>7284454</v>
+        <v>7284315</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3308,10 +3308,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>127148055</v>
+        <v>127148038</v>
       </c>
       <c r="B29" t="n">
-        <v>92640</v>
+        <v>97989</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3319,21 +3319,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>718732</v>
+        <v>718694</v>
       </c>
       <c r="R29" t="n">
-        <v>7284447</v>
+        <v>7284325</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3405,10 +3405,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>127148043</v>
+        <v>127148039</v>
       </c>
       <c r="B30" t="n">
-        <v>97351</v>
+        <v>97989</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3440,10 +3440,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>718667</v>
+        <v>718678</v>
       </c>
       <c r="R30" t="n">
-        <v>7284313</v>
+        <v>7284335</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3502,10 +3502,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>127148035</v>
+        <v>127148040</v>
       </c>
       <c r="B31" t="n">
-        <v>97351</v>
+        <v>97989</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3537,10 +3537,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>718776</v>
+        <v>718660</v>
       </c>
       <c r="R31" t="n">
-        <v>7284309</v>
+        <v>7284356</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3599,32 +3599,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>127148020</v>
+        <v>127148041</v>
       </c>
       <c r="B32" t="n">
-        <v>79647</v>
+        <v>97989</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6453</v>
+        <v>221941</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3634,10 +3634,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>718765</v>
+        <v>718660</v>
       </c>
       <c r="R32" t="n">
-        <v>7284389</v>
+        <v>7284340</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -3696,10 +3696,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>127148061</v>
+        <v>127148042</v>
       </c>
       <c r="B33" t="n">
-        <v>92640</v>
+        <v>97989</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3707,21 +3707,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>221941</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3731,10 +3731,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>718771</v>
+        <v>718677</v>
       </c>
       <c r="R33" t="n">
-        <v>7284306</v>
+        <v>7284327</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -3793,32 +3793,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>127148030</v>
+        <v>127148043</v>
       </c>
       <c r="B34" t="n">
-        <v>57669</v>
+        <v>97989</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100049</v>
+        <v>221941</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3828,10 +3828,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>718687</v>
+        <v>718667</v>
       </c>
       <c r="R34" t="n">
-        <v>7284276</v>
+        <v>7284313</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -3887,6 +3887,394 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>127148046</v>
+      </c>
+      <c r="B35" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Grisberget, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>718742</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7284376</v>
+      </c>
+      <c r="S35" t="n">
+        <v>5</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>127148027</v>
+      </c>
+      <c r="B36" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Grisberget, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>718732</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7284388</v>
+      </c>
+      <c r="S36" t="n">
+        <v>5</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>127148028</v>
+      </c>
+      <c r="B37" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Grisberget, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>718689</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7284386</v>
+      </c>
+      <c r="S37" t="n">
+        <v>5</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>127148029</v>
+      </c>
+      <c r="B38" t="n">
+        <v>79350</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Grisberget, Pi lm</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>718742</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7284355</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Pite lappmark</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Arvidsjaur</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-08-03</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 58862-2024 artfynd.xlsx
+++ b/artfynd/A 58862-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AZ38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127148051</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -867,6 +877,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127148031</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127148067</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1065,6 +1085,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127148054</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,6 +1187,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127148055</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1259,6 +1289,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127148056</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1356,6 +1391,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127148057</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1453,6 +1493,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127148058</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1550,6 +1595,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127148059</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1647,6 +1697,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127148060</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1744,6 +1799,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127148061</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1841,6 +1901,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127148062</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1938,6 +2003,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127148063</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2035,6 +2105,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127148064</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2132,6 +2207,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127148065</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2229,6 +2309,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127148068</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2326,6 +2411,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127148020</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2423,6 +2513,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127148021</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2520,6 +2615,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127148045</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2617,6 +2717,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127148030</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2723,6 +2828,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127148022</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2820,6 +2930,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127148044</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2917,6 +3032,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127148032</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3014,6 +3134,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127148033</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3111,6 +3236,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127148034</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3208,6 +3338,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127148035</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3305,6 +3440,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127148036</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3402,6 +3542,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127148038</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3499,6 +3644,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127148039</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3596,6 +3746,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127148040</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3693,6 +3848,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127148041</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3790,6 +3950,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127148042</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3887,6 +4052,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127148043</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -3984,6 +4154,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127148046</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4081,6 +4256,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127148027</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4178,6 +4358,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127148028</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4275,8 +4460,52 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127148029</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>